--- a/files/Controller Design/ZNMethods_ITAE_Errors.xlsx
+++ b/files/Controller Design/ZNMethods_ITAE_Errors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulisboa-my.sharepoint.com/personal/ist1100262_tecnico_ulisboa_pt/Documents/MEMec/Thesis/files/Controller Design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="669" documentId="8_{95F32091-D855-4402-ADD3-8991BE5FE270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE4E4AD9-B79F-492F-85CB-9B28319C3CDB}"/>
+  <xr:revisionPtr revIDLastSave="673" documentId="8_{95F32091-D855-4402-ADD3-8991BE5FE270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66A97C0E-F44F-421D-A080-449570F88324}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" tabRatio="617" activeTab="4" xr2:uid="{6BCB78A0-0C46-4270-8084-079A19E30873}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" tabRatio="617" activeTab="7" xr2:uid="{6BCB78A0-0C46-4270-8084-079A19E30873}"/>
   </bookViews>
   <sheets>
     <sheet name="ZNMethods" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="55">
   <si>
     <t>ν/ζ</t>
   </si>
@@ -133,9 +133,6 @@
     <t>Simulations kept over 30 seconds</t>
   </si>
   <si>
-    <t>Noise level 0.01 no filter</t>
-  </si>
-  <si>
     <t>ITAE Error</t>
   </si>
   <si>
@@ -212,6 +209,9 @@
   </si>
   <si>
     <t>sucess rate</t>
+  </si>
+  <si>
+    <t>Noise level 0.01 filtered</t>
   </si>
 </sst>
 </file>
@@ -868,6 +868,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -886,19 +899,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1340,36 +1340,36 @@
   <sheetData>
     <row r="1" spans="2:28" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="77"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="88"/>
     </row>
     <row r="3" spans="2:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="74"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="85"/>
     </row>
     <row r="5" spans="2:28" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="73"/>
-      <c r="D6" s="74"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="85"/>
       <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="P6" s="83" t="s">
         <v>44</v>
       </c>
-      <c r="P6" s="72" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q6" s="73"/>
-      <c r="R6" s="74"/>
+      <c r="Q6" s="84"/>
+      <c r="R6" s="85"/>
     </row>
     <row r="7" spans="2:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="19" t="s">
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AB12" s="4">
         <v>1.2338</v>
@@ -1921,7 +1921,7 @@
         <v>1.4329000000000001</v>
       </c>
       <c r="AA13" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AB13" s="4">
         <v>6.4298999999999999</v>
@@ -2107,11 +2107,11 @@
       <c r="Z18" s="70"/>
     </row>
     <row r="19" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="72" t="s">
+      <c r="B19" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="73"/>
-      <c r="D19" s="74"/>
+      <c r="C19" s="84"/>
+      <c r="D19" s="85"/>
     </row>
     <row r="20" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="19" t="s">
@@ -2358,7 +2358,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N25" s="4">
         <v>1.2262999999999999</v>
@@ -2399,7 +2399,7 @@
         <v>1</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N26" s="4">
         <v>0.70089999999999997</v>
@@ -2498,16 +2498,16 @@
     </row>
     <row r="30" spans="2:26" x14ac:dyDescent="0.3">
       <c r="S30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="32" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="72" t="s">
+      <c r="B32" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="73"/>
-      <c r="D32" s="74"/>
+      <c r="C32" s="84"/>
+      <c r="D32" s="85"/>
     </row>
     <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="19" t="s">
@@ -3050,13 +3050,13 @@
   <sheetData>
     <row r="1" spans="2:97" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="BQ1" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="BQ1" s="55" t="s">
-        <v>39</v>
-      </c>
       <c r="CF1" s="55" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="2:97" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
@@ -3211,7 +3211,7 @@
         <v>5</v>
       </c>
       <c r="BB2" s="40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="BC2" s="41">
         <v>0.7</v>
@@ -3253,7 +3253,7 @@
         <v>1.9</v>
       </c>
       <c r="BQ2" s="35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="BR2" s="36">
         <v>0.7</v>
@@ -3295,7 +3295,7 @@
         <v>1.9</v>
       </c>
       <c r="CF2" s="35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="CG2" s="36">
         <v>0.7</v>
@@ -6956,7 +6956,7 @@
         <v>24</v>
       </c>
       <c r="P16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R16">
         <f>AVERAGE(C3:AY15)</f>
@@ -7347,7 +7347,7 @@
     </row>
     <row r="19" spans="2:97" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BB19" s="48">
         <v>1.9</v>
@@ -11370,10 +11370,10 @@
     </row>
     <row r="34" spans="2:97" ht="21" x14ac:dyDescent="0.4">
       <c r="B34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34" s="39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F34" s="60">
         <f>AVERAGE(C21:AY33)</f>
@@ -11764,7 +11764,7 @@
     </row>
     <row r="37" spans="2:97" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BB37" s="48">
         <v>3.7</v>
@@ -15661,7 +15661,7 @@
     </row>
     <row r="52" spans="2:97" x14ac:dyDescent="0.35">
       <c r="E52" s="39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F52">
         <f>AVERAGE(C39:AY51)</f>
@@ -27222,12 +27222,12 @@
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -27260,7 +27260,7 @@
   <sheetData>
     <row r="1" spans="2:67" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="2:67" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -27414,46 +27414,46 @@
       <c r="AY2" s="1">
         <v>5</v>
       </c>
-      <c r="BB2" s="78" t="s">
-        <v>37</v>
-      </c>
-      <c r="BC2" s="79">
+      <c r="BB2" s="72" t="s">
+        <v>36</v>
+      </c>
+      <c r="BC2" s="73">
         <v>0.7</v>
       </c>
-      <c r="BD2" s="80">
+      <c r="BD2" s="74">
         <v>0.8</v>
       </c>
-      <c r="BE2" s="80">
+      <c r="BE2" s="74">
         <v>0.9</v>
       </c>
-      <c r="BF2" s="80">
-        <v>1</v>
-      </c>
-      <c r="BG2" s="80">
+      <c r="BF2" s="74">
+        <v>1</v>
+      </c>
+      <c r="BG2" s="74">
         <v>1.1000000000000001</v>
       </c>
-      <c r="BH2" s="80">
+      <c r="BH2" s="74">
         <v>1.2</v>
       </c>
-      <c r="BI2" s="80">
+      <c r="BI2" s="74">
         <v>1.3</v>
       </c>
-      <c r="BJ2" s="80">
+      <c r="BJ2" s="74">
         <v>1.4</v>
       </c>
-      <c r="BK2" s="80">
+      <c r="BK2" s="74">
         <v>1.5</v>
       </c>
-      <c r="BL2" s="80">
+      <c r="BL2" s="74">
         <v>1.6</v>
       </c>
-      <c r="BM2" s="80">
+      <c r="BM2" s="74">
         <v>1.7</v>
       </c>
-      <c r="BN2" s="80">
+      <c r="BN2" s="74">
         <v>1.8</v>
       </c>
-      <c r="BO2" s="81">
+      <c r="BO2" s="75">
         <v>1.9</v>
       </c>
     </row>
@@ -27608,46 +27608,46 @@
       <c r="AY3" s="1">
         <v>0.2349</v>
       </c>
-      <c r="BB3" s="82">
+      <c r="BB3" s="76">
         <v>0.3</v>
       </c>
-      <c r="BC3" s="83">
+      <c r="BC3" s="77">
         <v>0.1075</v>
       </c>
-      <c r="BD3" s="83">
+      <c r="BD3" s="77">
         <v>0.1595</v>
       </c>
-      <c r="BE3" s="83">
+      <c r="BE3" s="77">
         <v>0.2054</v>
       </c>
-      <c r="BF3" s="83">
+      <c r="BF3" s="77">
         <v>0.23669999999999999</v>
       </c>
-      <c r="BG3" s="83">
+      <c r="BG3" s="77">
         <v>0.25580000000000003</v>
       </c>
-      <c r="BH3" s="83">
+      <c r="BH3" s="77">
         <v>0.26240000000000002</v>
       </c>
-      <c r="BI3" s="83">
+      <c r="BI3" s="77">
         <v>0.59760000000000002</v>
       </c>
-      <c r="BJ3" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BK3" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BL3" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BM3" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BN3" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BO3" s="84" t="s">
+      <c r="BJ3" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BK3" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BL3" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BM3" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BN3" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BO3" s="78" t="s">
         <v>10</v>
       </c>
     </row>
@@ -27802,46 +27802,46 @@
       <c r="AY4" s="1">
         <v>0.4128</v>
       </c>
-      <c r="BB4" s="85">
+      <c r="BB4" s="79">
         <v>0.4</v>
       </c>
-      <c r="BC4" s="83">
+      <c r="BC4" s="77">
         <v>0.1017</v>
       </c>
-      <c r="BD4" s="83">
+      <c r="BD4" s="77">
         <v>0.15920000000000001</v>
       </c>
-      <c r="BE4" s="83">
+      <c r="BE4" s="77">
         <v>0.20399999999999999</v>
       </c>
-      <c r="BF4" s="83">
+      <c r="BF4" s="77">
         <v>0.23449999999999999</v>
       </c>
-      <c r="BG4" s="83">
+      <c r="BG4" s="77">
         <v>0.2525</v>
       </c>
-      <c r="BH4" s="83">
+      <c r="BH4" s="77">
         <v>0.26150000000000001</v>
       </c>
-      <c r="BI4" s="83">
+      <c r="BI4" s="77">
         <v>0.41199999999999998</v>
       </c>
-      <c r="BJ4" s="83">
+      <c r="BJ4" s="77">
         <v>0.55449999999999999</v>
       </c>
-      <c r="BK4" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BL4" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BM4" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BN4" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BO4" s="84" t="s">
+      <c r="BK4" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BL4" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BM4" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BN4" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BO4" s="78" t="s">
         <v>10</v>
       </c>
     </row>
@@ -27996,46 +27996,46 @@
       <c r="AY5" s="1">
         <v>0.68189999999999995</v>
       </c>
-      <c r="BB5" s="85">
+      <c r="BB5" s="79">
         <v>0.5</v>
       </c>
-      <c r="BC5" s="83">
+      <c r="BC5" s="77">
         <v>9.8199999999999996E-2</v>
       </c>
-      <c r="BD5" s="83">
+      <c r="BD5" s="77">
         <v>0.15909999999999999</v>
       </c>
-      <c r="BE5" s="83">
+      <c r="BE5" s="77">
         <v>0.20269999999999999</v>
       </c>
-      <c r="BF5" s="83">
+      <c r="BF5" s="77">
         <v>0.23230000000000001</v>
       </c>
-      <c r="BG5" s="83">
+      <c r="BG5" s="77">
         <v>0.24929999999999999</v>
       </c>
-      <c r="BH5" s="83">
+      <c r="BH5" s="77">
         <v>0.26169999999999999</v>
       </c>
-      <c r="BI5" s="83">
+      <c r="BI5" s="77">
         <v>0.32</v>
       </c>
-      <c r="BJ5" s="83">
+      <c r="BJ5" s="77">
         <v>0.33229999999999998</v>
       </c>
-      <c r="BK5" s="83">
+      <c r="BK5" s="77">
         <v>0.37819999999999998</v>
       </c>
-      <c r="BL5" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BM5" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BN5" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BO5" s="84" t="s">
+      <c r="BL5" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BM5" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BN5" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BO5" s="78" t="s">
         <v>10</v>
       </c>
     </row>
@@ -28190,46 +28190,46 @@
       <c r="AY6" s="1">
         <v>0.60629999999999995</v>
       </c>
-      <c r="BB6" s="85">
+      <c r="BB6" s="79">
         <v>0.6</v>
       </c>
-      <c r="BC6" s="83">
+      <c r="BC6" s="77">
         <v>9.6600000000000005E-2</v>
       </c>
-      <c r="BD6" s="83">
+      <c r="BD6" s="77">
         <v>0.159</v>
       </c>
-      <c r="BE6" s="83">
+      <c r="BE6" s="77">
         <v>0.2014</v>
       </c>
-      <c r="BF6" s="83">
+      <c r="BF6" s="77">
         <v>0.2301</v>
       </c>
-      <c r="BG6" s="83">
+      <c r="BG6" s="77">
         <v>0.247</v>
       </c>
-      <c r="BH6" s="83">
+      <c r="BH6" s="77">
         <v>0.26190000000000002</v>
       </c>
-      <c r="BI6" s="83">
+      <c r="BI6" s="77">
         <v>0.28199999999999997</v>
       </c>
-      <c r="BJ6" s="83">
+      <c r="BJ6" s="77">
         <v>0.2409</v>
       </c>
-      <c r="BK6" s="83">
+      <c r="BK6" s="77">
         <v>0.21260000000000001</v>
       </c>
-      <c r="BL6" s="83">
+      <c r="BL6" s="77">
         <v>0.4204</v>
       </c>
-      <c r="BM6" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BN6" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BO6" s="84" t="s">
+      <c r="BM6" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BN6" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BO6" s="78" t="s">
         <v>10</v>
       </c>
     </row>
@@ -28384,46 +28384,46 @@
       <c r="AY7" s="1">
         <v>0.3906</v>
       </c>
-      <c r="BB7" s="85">
+      <c r="BB7" s="79">
         <v>0.7</v>
       </c>
-      <c r="BC7" s="83">
+      <c r="BC7" s="77">
         <v>9.7600000000000006E-2</v>
       </c>
-      <c r="BD7" s="83">
+      <c r="BD7" s="77">
         <v>0.15909999999999999</v>
       </c>
-      <c r="BE7" s="83">
+      <c r="BE7" s="77">
         <v>0.2001</v>
       </c>
-      <c r="BF7" s="83">
+      <c r="BF7" s="77">
         <v>0.22800000000000001</v>
       </c>
-      <c r="BG7" s="83">
+      <c r="BG7" s="77">
         <v>0.246</v>
       </c>
-      <c r="BH7" s="83">
+      <c r="BH7" s="77">
         <v>0.26100000000000001</v>
       </c>
-      <c r="BI7" s="83">
+      <c r="BI7" s="77">
         <v>0.26240000000000002</v>
       </c>
-      <c r="BJ7" s="83">
+      <c r="BJ7" s="77">
         <v>0.2084</v>
       </c>
-      <c r="BK7" s="83">
+      <c r="BK7" s="77">
         <v>0.18029999999999999</v>
       </c>
-      <c r="BL7" s="83">
+      <c r="BL7" s="77">
         <v>0.25540000000000002</v>
       </c>
-      <c r="BM7" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BN7" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BO7" s="84" t="s">
+      <c r="BM7" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BN7" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BO7" s="78" t="s">
         <v>10</v>
       </c>
     </row>
@@ -28578,46 +28578,46 @@
       <c r="AY8" s="1">
         <v>0.2626</v>
       </c>
-      <c r="BB8" s="85">
+      <c r="BB8" s="79">
         <v>0.8</v>
       </c>
-      <c r="BC8" s="83">
+      <c r="BC8" s="77">
         <v>0.1004</v>
       </c>
-      <c r="BD8" s="83">
+      <c r="BD8" s="77">
         <v>0.15939999999999999</v>
       </c>
-      <c r="BE8" s="83">
+      <c r="BE8" s="77">
         <v>0.19900000000000001</v>
       </c>
-      <c r="BF8" s="83">
+      <c r="BF8" s="77">
         <v>0.22600000000000001</v>
       </c>
-      <c r="BG8" s="83">
+      <c r="BG8" s="77">
         <v>0.24460000000000001</v>
       </c>
-      <c r="BH8" s="83">
+      <c r="BH8" s="77">
         <v>0.2581</v>
       </c>
-      <c r="BI8" s="83">
+      <c r="BI8" s="77">
         <v>0.24529999999999999</v>
       </c>
-      <c r="BJ8" s="83">
+      <c r="BJ8" s="77">
         <v>0.19209999999999999</v>
       </c>
-      <c r="BK8" s="83">
+      <c r="BK8" s="77">
         <v>0.1658</v>
       </c>
-      <c r="BL8" s="83">
+      <c r="BL8" s="77">
         <v>0.22739999999999999</v>
       </c>
-      <c r="BM8" s="83">
+      <c r="BM8" s="77">
         <v>0.52990000000000004</v>
       </c>
-      <c r="BN8" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BO8" s="84" t="s">
+      <c r="BN8" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BO8" s="78" t="s">
         <v>10</v>
       </c>
     </row>
@@ -28772,46 +28772,46 @@
       <c r="AY9" s="1">
         <v>0.2261</v>
       </c>
-      <c r="BB9" s="85">
+      <c r="BB9" s="79">
         <v>0.9</v>
       </c>
-      <c r="BC9" s="83">
+      <c r="BC9" s="77">
         <v>0.1033</v>
       </c>
-      <c r="BD9" s="83">
+      <c r="BD9" s="77">
         <v>0.15970000000000001</v>
       </c>
-      <c r="BE9" s="83">
+      <c r="BE9" s="77">
         <v>0.19800000000000001</v>
       </c>
-      <c r="BF9" s="83">
+      <c r="BF9" s="77">
         <v>0.2243</v>
       </c>
-      <c r="BG9" s="83">
+      <c r="BG9" s="77">
         <v>0.24249999999999999</v>
       </c>
-      <c r="BH9" s="83">
+      <c r="BH9" s="77">
         <v>0.25380000000000003</v>
       </c>
-      <c r="BI9" s="83">
+      <c r="BI9" s="77">
         <v>0.2344</v>
       </c>
-      <c r="BJ9" s="83">
+      <c r="BJ9" s="77">
         <v>0.17960000000000001</v>
       </c>
-      <c r="BK9" s="83">
+      <c r="BK9" s="77">
         <v>0.15329999999999999</v>
       </c>
-      <c r="BL9" s="83">
+      <c r="BL9" s="77">
         <v>0.20619999999999999</v>
       </c>
-      <c r="BM9" s="83">
+      <c r="BM9" s="77">
         <v>0.41799999999999998</v>
       </c>
-      <c r="BN9" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BO9" s="84" t="s">
+      <c r="BN9" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BO9" s="78" t="s">
         <v>10</v>
       </c>
     </row>
@@ -28966,46 +28966,46 @@
       <c r="AY10" s="1">
         <v>0.25519999999999998</v>
       </c>
-      <c r="BB10" s="85">
-        <v>1</v>
-      </c>
-      <c r="BC10" s="83">
+      <c r="BB10" s="79">
+        <v>1</v>
+      </c>
+      <c r="BC10" s="77">
         <v>0.1062</v>
       </c>
-      <c r="BD10" s="83">
+      <c r="BD10" s="77">
         <v>0.1603</v>
       </c>
-      <c r="BE10" s="83">
+      <c r="BE10" s="77">
         <v>0.19719999999999999</v>
       </c>
-      <c r="BF10" s="83">
+      <c r="BF10" s="77">
         <v>0.2228</v>
       </c>
-      <c r="BG10" s="83">
+      <c r="BG10" s="77">
         <v>0.24</v>
       </c>
-      <c r="BH10" s="83">
+      <c r="BH10" s="77">
         <v>0.2487</v>
       </c>
-      <c r="BI10" s="83">
+      <c r="BI10" s="77">
         <v>0.22589999999999999</v>
       </c>
-      <c r="BJ10" s="83">
+      <c r="BJ10" s="77">
         <v>0.1701</v>
       </c>
-      <c r="BK10" s="83">
+      <c r="BK10" s="77">
         <v>0.14299999999999999</v>
       </c>
-      <c r="BL10" s="83">
+      <c r="BL10" s="77">
         <v>0.19009999999999999</v>
       </c>
-      <c r="BM10" s="83">
+      <c r="BM10" s="77">
         <v>0.38840000000000002</v>
       </c>
-      <c r="BN10" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="BO10" s="84" t="s">
+      <c r="BN10" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="BO10" s="78" t="s">
         <v>10</v>
       </c>
     </row>
@@ -29160,46 +29160,46 @@
       <c r="AY11" s="27">
         <v>0.31180000000000002</v>
       </c>
-      <c r="BB11" s="85">
+      <c r="BB11" s="79">
         <v>1.1000000000000001</v>
       </c>
-      <c r="BC11" s="83">
+      <c r="BC11" s="77">
         <v>0.10920000000000001</v>
       </c>
-      <c r="BD11" s="83">
+      <c r="BD11" s="77">
         <v>0.161</v>
       </c>
-      <c r="BE11" s="83">
+      <c r="BE11" s="77">
         <v>0.1966</v>
       </c>
-      <c r="BF11" s="83">
+      <c r="BF11" s="77">
         <v>0.22159999999999999</v>
       </c>
-      <c r="BG11" s="83">
+      <c r="BG11" s="77">
         <v>0.23730000000000001</v>
       </c>
-      <c r="BH11" s="83">
+      <c r="BH11" s="77">
         <v>0.2432</v>
       </c>
-      <c r="BI11" s="83">
+      <c r="BI11" s="77">
         <v>0.2175</v>
       </c>
-      <c r="BJ11" s="83">
+      <c r="BJ11" s="77">
         <v>0.1623</v>
       </c>
-      <c r="BK11" s="83">
+      <c r="BK11" s="77">
         <v>0.13489999999999999</v>
       </c>
-      <c r="BL11" s="83">
+      <c r="BL11" s="77">
         <v>0.1832</v>
       </c>
-      <c r="BM11" s="83">
+      <c r="BM11" s="77">
         <v>0.38790000000000002</v>
       </c>
-      <c r="BN11" s="83">
+      <c r="BN11" s="77">
         <v>1.1256999999999999</v>
       </c>
-      <c r="BO11" s="84" t="s">
+      <c r="BO11" s="78" t="s">
         <v>10</v>
       </c>
     </row>
@@ -29354,46 +29354,46 @@
       <c r="AY12" s="1">
         <v>0.1157</v>
       </c>
-      <c r="BB12" s="85">
+      <c r="BB12" s="79">
         <v>1.2</v>
       </c>
-      <c r="BC12" s="83">
+      <c r="BC12" s="77">
         <v>0.11219999999999999</v>
       </c>
-      <c r="BD12" s="83">
+      <c r="BD12" s="77">
         <v>0.1618</v>
       </c>
-      <c r="BE12" s="83">
+      <c r="BE12" s="77">
         <v>0.19620000000000001</v>
       </c>
-      <c r="BF12" s="83">
+      <c r="BF12" s="77">
         <v>0.22059999999999999</v>
       </c>
-      <c r="BG12" s="83">
+      <c r="BG12" s="77">
         <v>0.23499999999999999</v>
       </c>
-      <c r="BH12" s="83">
+      <c r="BH12" s="77">
         <v>0.23769999999999999</v>
       </c>
-      <c r="BI12" s="83">
+      <c r="BI12" s="77">
         <v>0.20930000000000001</v>
       </c>
-      <c r="BJ12" s="83">
+      <c r="BJ12" s="77">
         <v>0.1547</v>
       </c>
-      <c r="BK12" s="83">
+      <c r="BK12" s="77">
         <v>0.12720000000000001</v>
       </c>
-      <c r="BL12" s="83">
+      <c r="BL12" s="77">
         <v>0.17749999999999999</v>
       </c>
-      <c r="BM12" s="83">
+      <c r="BM12" s="77">
         <v>0.38979999999999998</v>
       </c>
-      <c r="BN12" s="83">
+      <c r="BN12" s="77">
         <v>0.89529999999999998</v>
       </c>
-      <c r="BO12" s="84" t="s">
+      <c r="BO12" s="78" t="s">
         <v>10</v>
       </c>
     </row>
@@ -29548,46 +29548,46 @@
       <c r="AY13" s="1">
         <v>1.0588</v>
       </c>
-      <c r="BB13" s="85">
+      <c r="BB13" s="79">
         <v>1.3</v>
       </c>
-      <c r="BC13" s="83">
+      <c r="BC13" s="77">
         <v>0.11509999999999999</v>
       </c>
-      <c r="BD13" s="83">
+      <c r="BD13" s="77">
         <v>0.1628</v>
       </c>
-      <c r="BE13" s="83">
+      <c r="BE13" s="77">
         <v>0.19600000000000001</v>
       </c>
-      <c r="BF13" s="83">
+      <c r="BF13" s="77">
         <v>0.22009999999999999</v>
       </c>
-      <c r="BG13" s="83">
+      <c r="BG13" s="77">
         <v>0.2339</v>
       </c>
-      <c r="BH13" s="83">
+      <c r="BH13" s="77">
         <v>0.2326</v>
       </c>
-      <c r="BI13" s="83">
+      <c r="BI13" s="77">
         <v>0.20150000000000001</v>
       </c>
-      <c r="BJ13" s="83">
+      <c r="BJ13" s="77">
         <v>0.14749999999999999</v>
       </c>
-      <c r="BK13" s="83">
+      <c r="BK13" s="77">
         <v>0.1212</v>
       </c>
-      <c r="BL13" s="83">
+      <c r="BL13" s="77">
         <v>0.1724</v>
       </c>
-      <c r="BM13" s="83">
+      <c r="BM13" s="77">
         <v>0.38200000000000001</v>
       </c>
-      <c r="BN13" s="83">
+      <c r="BN13" s="77">
         <v>0.80600000000000005</v>
       </c>
-      <c r="BO13" s="84" t="s">
+      <c r="BO13" s="78" t="s">
         <v>10</v>
       </c>
     </row>
@@ -29742,46 +29742,46 @@
       <c r="AY14" s="1">
         <v>1.7345999999999999</v>
       </c>
-      <c r="BB14" s="85">
+      <c r="BB14" s="79">
         <v>1.4</v>
       </c>
-      <c r="BC14" s="83">
+      <c r="BC14" s="77">
         <v>0.11799999999999999</v>
       </c>
-      <c r="BD14" s="83">
+      <c r="BD14" s="77">
         <v>0.1638</v>
       </c>
-      <c r="BE14" s="83">
+      <c r="BE14" s="77">
         <v>0.1961</v>
       </c>
-      <c r="BF14" s="83">
+      <c r="BF14" s="77">
         <v>0.21990000000000001</v>
       </c>
-      <c r="BG14" s="83">
+      <c r="BG14" s="77">
         <v>0.2341</v>
       </c>
-      <c r="BH14" s="83">
+      <c r="BH14" s="77">
         <v>0.2288</v>
       </c>
-      <c r="BI14" s="83">
+      <c r="BI14" s="77">
         <v>0.19470000000000001</v>
       </c>
-      <c r="BJ14" s="83">
+      <c r="BJ14" s="77">
         <v>0.1409</v>
       </c>
-      <c r="BK14" s="83">
+      <c r="BK14" s="77">
         <v>0.1168</v>
       </c>
-      <c r="BL14" s="83">
+      <c r="BL14" s="77">
         <v>0.16980000000000001</v>
       </c>
-      <c r="BM14" s="83">
+      <c r="BM14" s="77">
         <v>0.36730000000000002</v>
       </c>
-      <c r="BN14" s="83">
+      <c r="BN14" s="77">
         <v>0.8105</v>
       </c>
-      <c r="BO14" s="84" t="s">
+      <c r="BO14" s="78" t="s">
         <v>10</v>
       </c>
     </row>
@@ -29936,1593 +29936,1593 @@
       <c r="AY15" s="1">
         <v>0.65490000000000004</v>
       </c>
-      <c r="BB15" s="85">
+      <c r="BB15" s="79">
         <v>1.5</v>
       </c>
-      <c r="BC15" s="83">
+      <c r="BC15" s="77">
         <v>0.1207</v>
       </c>
-      <c r="BD15" s="83">
+      <c r="BD15" s="77">
         <v>0.16500000000000001</v>
       </c>
-      <c r="BE15" s="83">
+      <c r="BE15" s="77">
         <v>0.19650000000000001</v>
       </c>
-      <c r="BF15" s="83">
+      <c r="BF15" s="77">
         <v>0.22009999999999999</v>
       </c>
-      <c r="BG15" s="83">
+      <c r="BG15" s="77">
         <v>0.2349</v>
       </c>
-      <c r="BH15" s="83">
+      <c r="BH15" s="77">
         <v>0.22839999999999999</v>
       </c>
-      <c r="BI15" s="83">
+      <c r="BI15" s="77">
         <v>0.1903</v>
       </c>
-      <c r="BJ15" s="83">
+      <c r="BJ15" s="77">
         <v>0.1356</v>
       </c>
-      <c r="BK15" s="83">
+      <c r="BK15" s="77">
         <v>0.1192</v>
       </c>
-      <c r="BL15" s="83">
+      <c r="BL15" s="77">
         <v>0.1729</v>
       </c>
-      <c r="BM15" s="83">
+      <c r="BM15" s="77">
         <v>0.35060000000000002</v>
       </c>
-      <c r="BN15" s="83">
+      <c r="BN15" s="77">
         <v>0.83550000000000002</v>
       </c>
-      <c r="BO15" s="84" t="s">
+      <c r="BO15" s="78" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="2:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB16" s="85">
+      <c r="BB16" s="79">
         <v>1.6</v>
       </c>
-      <c r="BC16" s="83">
+      <c r="BC16" s="77">
         <v>0.12330000000000001</v>
       </c>
-      <c r="BD16" s="83">
+      <c r="BD16" s="77">
         <v>0.1661</v>
       </c>
-      <c r="BE16" s="83">
+      <c r="BE16" s="77">
         <v>0.1971</v>
       </c>
-      <c r="BF16" s="83">
+      <c r="BF16" s="77">
         <v>0.2208</v>
       </c>
-      <c r="BG16" s="83">
+      <c r="BG16" s="77">
         <v>0.23630000000000001</v>
       </c>
-      <c r="BH16" s="83">
+      <c r="BH16" s="77">
         <v>0.2306</v>
       </c>
-      <c r="BI16" s="83">
+      <c r="BI16" s="77">
         <v>0.19109999999999999</v>
       </c>
-      <c r="BJ16" s="83">
+      <c r="BJ16" s="77">
         <v>0.13339999999999999</v>
       </c>
-      <c r="BK16" s="83">
+      <c r="BK16" s="77">
         <v>0.1241</v>
       </c>
-      <c r="BL16" s="83">
+      <c r="BL16" s="77">
         <v>0.18</v>
       </c>
-      <c r="BM16" s="83">
+      <c r="BM16" s="77">
         <v>0.33610000000000001</v>
       </c>
-      <c r="BN16" s="83">
+      <c r="BN16" s="77">
         <v>0.85360000000000003</v>
       </c>
-      <c r="BO16" s="84" t="s">
+      <c r="BO16" s="78" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="3:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB17" s="85">
+      <c r="BB17" s="79">
         <v>1.7</v>
       </c>
-      <c r="BC17" s="83">
+      <c r="BC17" s="77">
         <v>0.12570000000000001</v>
       </c>
-      <c r="BD17" s="83">
+      <c r="BD17" s="77">
         <v>0.1673</v>
       </c>
-      <c r="BE17" s="83">
+      <c r="BE17" s="77">
         <v>0.1978</v>
       </c>
-      <c r="BF17" s="83">
+      <c r="BF17" s="77">
         <v>0.2218</v>
       </c>
-      <c r="BG17" s="83">
+      <c r="BG17" s="77">
         <v>0.23830000000000001</v>
       </c>
-      <c r="BH17" s="83">
+      <c r="BH17" s="77">
         <v>0.2336</v>
       </c>
-      <c r="BI17" s="83">
+      <c r="BI17" s="77">
         <v>0.19350000000000001</v>
       </c>
-      <c r="BJ17" s="83">
+      <c r="BJ17" s="77">
         <v>0.13289999999999999</v>
       </c>
-      <c r="BK17" s="83">
+      <c r="BK17" s="77">
         <v>0.13250000000000001</v>
       </c>
-      <c r="BL17" s="83">
+      <c r="BL17" s="77">
         <v>0.18720000000000001</v>
       </c>
-      <c r="BM17" s="83">
+      <c r="BM17" s="77">
         <v>0.32690000000000002</v>
       </c>
-      <c r="BN17" s="83">
+      <c r="BN17" s="77">
         <v>0.86160000000000003</v>
       </c>
-      <c r="BO17" s="84">
+      <c r="BO17" s="78">
         <v>5.5648</v>
       </c>
     </row>
     <row r="18" spans="3:67" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18">
         <f>AVERAGE(C3:AY15)</f>
         <v>0.34505309882747082</v>
       </c>
-      <c r="BB18" s="85">
+      <c r="BB18" s="79">
         <v>1.8</v>
       </c>
-      <c r="BC18" s="83">
+      <c r="BC18" s="77">
         <v>0.12790000000000001</v>
       </c>
-      <c r="BD18" s="83">
+      <c r="BD18" s="77">
         <v>0.16850000000000001</v>
       </c>
-      <c r="BE18" s="83">
+      <c r="BE18" s="77">
         <v>0.1988</v>
       </c>
-      <c r="BF18" s="83">
+      <c r="BF18" s="77">
         <v>0.22320000000000001</v>
       </c>
-      <c r="BG18" s="83">
+      <c r="BG18" s="77">
         <v>0.2409</v>
       </c>
-      <c r="BH18" s="83">
+      <c r="BH18" s="77">
         <v>0.23760000000000001</v>
       </c>
-      <c r="BI18" s="83">
+      <c r="BI18" s="77">
         <v>0.19700000000000001</v>
       </c>
-      <c r="BJ18" s="83">
+      <c r="BJ18" s="77">
         <v>0.13350000000000001</v>
       </c>
-      <c r="BK18" s="83">
+      <c r="BK18" s="77">
         <v>0.14399999999999999</v>
       </c>
-      <c r="BL18" s="83">
+      <c r="BL18" s="77">
         <v>0.1948</v>
       </c>
-      <c r="BM18" s="83">
+      <c r="BM18" s="77">
         <v>0.32329999999999998</v>
       </c>
-      <c r="BN18" s="83">
+      <c r="BN18" s="77">
         <v>0.85360000000000003</v>
       </c>
-      <c r="BO18" s="84">
+      <c r="BO18" s="78">
         <v>4.4135999999999997</v>
       </c>
     </row>
     <row r="19" spans="3:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB19" s="85">
+      <c r="BB19" s="79">
         <v>1.9</v>
       </c>
-      <c r="BC19" s="83">
+      <c r="BC19" s="77">
         <v>0.12970000000000001</v>
       </c>
-      <c r="BD19" s="83">
+      <c r="BD19" s="77">
         <v>0.16950000000000001</v>
       </c>
-      <c r="BE19" s="83">
+      <c r="BE19" s="77">
         <v>0.19989999999999999</v>
       </c>
-      <c r="BF19" s="83">
+      <c r="BF19" s="77">
         <v>0.22500000000000001</v>
       </c>
-      <c r="BG19" s="83">
+      <c r="BG19" s="77">
         <v>0.24410000000000001</v>
       </c>
-      <c r="BH19" s="83">
+      <c r="BH19" s="77">
         <v>0.2424</v>
       </c>
-      <c r="BI19" s="83">
+      <c r="BI19" s="77">
         <v>0.20169999999999999</v>
       </c>
-      <c r="BJ19" s="83">
+      <c r="BJ19" s="77">
         <v>0.1353</v>
       </c>
-      <c r="BK19" s="83">
+      <c r="BK19" s="77">
         <v>0.1547</v>
       </c>
-      <c r="BL19" s="83">
+      <c r="BL19" s="77">
         <v>0.20380000000000001</v>
       </c>
-      <c r="BM19" s="83">
+      <c r="BM19" s="77">
         <v>0.31809999999999999</v>
       </c>
-      <c r="BN19" s="83">
+      <c r="BN19" s="77">
         <v>0.82609999999999995</v>
       </c>
-      <c r="BO19" s="84">
+      <c r="BO19" s="78">
         <v>3.4727999999999999</v>
       </c>
     </row>
     <row r="20" spans="3:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB20" s="85">
+      <c r="BB20" s="79">
         <v>2</v>
       </c>
-      <c r="BC20" s="83">
+      <c r="BC20" s="77">
         <v>0.1313</v>
       </c>
-      <c r="BD20" s="83">
+      <c r="BD20" s="77">
         <v>0.17030000000000001</v>
       </c>
-      <c r="BE20" s="83">
+      <c r="BE20" s="77">
         <v>0.2011</v>
       </c>
-      <c r="BF20" s="83">
+      <c r="BF20" s="77">
         <v>0.22700000000000001</v>
       </c>
-      <c r="BG20" s="83">
+      <c r="BG20" s="77">
         <v>0.24779999999999999</v>
       </c>
-      <c r="BH20" s="83">
+      <c r="BH20" s="77">
         <v>0.248</v>
       </c>
-      <c r="BI20" s="83">
+      <c r="BI20" s="77">
         <v>0.2074</v>
       </c>
-      <c r="BJ20" s="83">
+      <c r="BJ20" s="77">
         <v>0.13919999999999999</v>
       </c>
-      <c r="BK20" s="83">
+      <c r="BK20" s="77">
         <v>0.16450000000000001</v>
       </c>
-      <c r="BL20" s="83">
+      <c r="BL20" s="77">
         <v>0.2137</v>
       </c>
-      <c r="BM20" s="83">
+      <c r="BM20" s="77">
         <v>0.31</v>
       </c>
-      <c r="BN20" s="83">
+      <c r="BN20" s="77">
         <v>0.78300000000000003</v>
       </c>
-      <c r="BO20" s="84">
+      <c r="BO20" s="78">
         <v>2.7079</v>
       </c>
     </row>
     <row r="21" spans="3:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB21" s="85">
+      <c r="BB21" s="79">
         <v>2.1</v>
       </c>
-      <c r="BC21" s="83">
+      <c r="BC21" s="77">
         <v>0.1326</v>
       </c>
-      <c r="BD21" s="83">
+      <c r="BD21" s="77">
         <v>0.1709</v>
       </c>
-      <c r="BE21" s="83">
+      <c r="BE21" s="77">
         <v>0.20230000000000001</v>
       </c>
-      <c r="BF21" s="83">
+      <c r="BF21" s="77">
         <v>0.22919999999999999</v>
       </c>
-      <c r="BG21" s="83">
+      <c r="BG21" s="77">
         <v>0.25180000000000002</v>
       </c>
-      <c r="BH21" s="83">
+      <c r="BH21" s="77">
         <v>0.25430000000000003</v>
       </c>
-      <c r="BI21" s="83">
+      <c r="BI21" s="77">
         <v>0.214</v>
       </c>
-      <c r="BJ21" s="83">
+      <c r="BJ21" s="77">
         <v>0.14940000000000001</v>
       </c>
-      <c r="BK21" s="83">
+      <c r="BK21" s="77">
         <v>0.1734</v>
       </c>
-      <c r="BL21" s="83">
+      <c r="BL21" s="77">
         <v>0.222</v>
       </c>
-      <c r="BM21" s="83">
+      <c r="BM21" s="77">
         <v>0.3004</v>
       </c>
-      <c r="BN21" s="83">
+      <c r="BN21" s="77">
         <v>0.73050000000000004</v>
       </c>
-      <c r="BO21" s="84">
+      <c r="BO21" s="78">
         <v>2.0996000000000001</v>
       </c>
     </row>
     <row r="22" spans="3:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB22" s="85">
+      <c r="BB22" s="79">
         <v>2.2000000000000002</v>
       </c>
-      <c r="BC22" s="83">
+      <c r="BC22" s="77">
         <v>0.13350000000000001</v>
       </c>
-      <c r="BD22" s="83">
+      <c r="BD22" s="77">
         <v>0.17119999999999999</v>
       </c>
-      <c r="BE22" s="83">
+      <c r="BE22" s="77">
         <v>0.2034</v>
       </c>
-      <c r="BF22" s="83">
+      <c r="BF22" s="77">
         <v>0.23150000000000001</v>
       </c>
-      <c r="BG22" s="83">
+      <c r="BG22" s="77">
         <v>0.25609999999999999</v>
       </c>
-      <c r="BH22" s="83">
+      <c r="BH22" s="77">
         <v>0.2611</v>
       </c>
-      <c r="BI22" s="83">
+      <c r="BI22" s="77">
         <v>0.22159999999999999</v>
       </c>
-      <c r="BJ22" s="83">
+      <c r="BJ22" s="77">
         <v>0.16009999999999999</v>
       </c>
-      <c r="BK22" s="83">
+      <c r="BK22" s="77">
         <v>0.1812</v>
       </c>
-      <c r="BL22" s="83">
+      <c r="BL22" s="77">
         <v>0.22869999999999999</v>
       </c>
-      <c r="BM22" s="83">
+      <c r="BM22" s="77">
         <v>0.29060000000000002</v>
       </c>
-      <c r="BN22" s="83">
+      <c r="BN22" s="77">
         <v>0.6754</v>
       </c>
-      <c r="BO22" s="84">
+      <c r="BO22" s="78">
         <v>1.6258999999999999</v>
       </c>
     </row>
     <row r="23" spans="3:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB23" s="85">
+      <c r="BB23" s="79">
         <v>2.2999999999999998</v>
       </c>
-      <c r="BC23" s="83">
+      <c r="BC23" s="77">
         <v>0.13400000000000001</v>
       </c>
-      <c r="BD23" s="83">
+      <c r="BD23" s="77">
         <v>0.1711</v>
       </c>
-      <c r="BE23" s="83">
+      <c r="BE23" s="77">
         <v>0.20430000000000001</v>
       </c>
-      <c r="BF23" s="83">
+      <c r="BF23" s="77">
         <v>0.23380000000000001</v>
       </c>
-      <c r="BG23" s="83">
+      <c r="BG23" s="77">
         <v>0.2606</v>
       </c>
-      <c r="BH23" s="83">
+      <c r="BH23" s="77">
         <v>0.26819999999999999</v>
       </c>
-      <c r="BI23" s="83">
+      <c r="BI23" s="77">
         <v>0.2298</v>
       </c>
-      <c r="BJ23" s="83">
+      <c r="BJ23" s="77">
         <v>0.17130000000000001</v>
       </c>
-      <c r="BK23" s="83">
+      <c r="BK23" s="77">
         <v>0.18779999999999999</v>
       </c>
-      <c r="BL23" s="83">
+      <c r="BL23" s="77">
         <v>0.23400000000000001</v>
       </c>
-      <c r="BM23" s="83">
+      <c r="BM23" s="77">
         <v>0.28120000000000001</v>
       </c>
-      <c r="BN23" s="83">
+      <c r="BN23" s="77">
         <v>0.62309999999999999</v>
       </c>
-      <c r="BO23" s="84">
+      <c r="BO23" s="78">
         <v>1.2617</v>
       </c>
     </row>
     <row r="24" spans="3:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB24" s="85">
+      <c r="BB24" s="79">
         <v>2.4</v>
       </c>
-      <c r="BC24" s="83">
+      <c r="BC24" s="77">
         <v>0.13420000000000001</v>
       </c>
-      <c r="BD24" s="83">
+      <c r="BD24" s="77">
         <v>0.17050000000000001</v>
       </c>
-      <c r="BE24" s="83">
+      <c r="BE24" s="77">
         <v>0.2049</v>
       </c>
-      <c r="BF24" s="83">
+      <c r="BF24" s="77">
         <v>0.23599999999999999</v>
       </c>
-      <c r="BG24" s="83">
+      <c r="BG24" s="77">
         <v>0.26490000000000002</v>
       </c>
-      <c r="BH24" s="83">
+      <c r="BH24" s="77">
         <v>0.27550000000000002</v>
       </c>
-      <c r="BI24" s="83">
+      <c r="BI24" s="77">
         <v>0.23849999999999999</v>
       </c>
-      <c r="BJ24" s="83">
+      <c r="BJ24" s="77">
         <v>0.18279999999999999</v>
       </c>
-      <c r="BK24" s="83">
+      <c r="BK24" s="77">
         <v>0.19320000000000001</v>
       </c>
-      <c r="BL24" s="83">
+      <c r="BL24" s="77">
         <v>0.2384</v>
       </c>
-      <c r="BM24" s="83">
+      <c r="BM24" s="77">
         <v>0.27229999999999999</v>
       </c>
-      <c r="BN24" s="83">
+      <c r="BN24" s="77">
         <v>0.57699999999999996</v>
       </c>
-      <c r="BO24" s="84">
+      <c r="BO24" s="78">
         <v>0.9839</v>
       </c>
     </row>
     <row r="25" spans="3:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB25" s="85">
+      <c r="BB25" s="79">
         <v>2.5</v>
       </c>
-      <c r="BC25" s="83">
+      <c r="BC25" s="77">
         <v>0.1341</v>
       </c>
-      <c r="BD25" s="83">
+      <c r="BD25" s="77">
         <v>0.1694</v>
       </c>
-      <c r="BE25" s="83">
+      <c r="BE25" s="77">
         <v>0.20519999999999999</v>
       </c>
-      <c r="BF25" s="83">
+      <c r="BF25" s="77">
         <v>0.23780000000000001</v>
       </c>
-      <c r="BG25" s="83">
+      <c r="BG25" s="77">
         <v>0.26910000000000001</v>
       </c>
-      <c r="BH25" s="83">
+      <c r="BH25" s="77">
         <v>0.2828</v>
       </c>
-      <c r="BI25" s="83">
+      <c r="BI25" s="77">
         <v>0.2475</v>
       </c>
-      <c r="BJ25" s="83">
+      <c r="BJ25" s="77">
         <v>0.19439999999999999</v>
       </c>
-      <c r="BK25" s="83">
+      <c r="BK25" s="77">
         <v>0.19739999999999999</v>
       </c>
-      <c r="BL25" s="83">
+      <c r="BL25" s="77">
         <v>0.24229999999999999</v>
       </c>
-      <c r="BM25" s="83">
+      <c r="BM25" s="77">
         <v>0.26350000000000001</v>
       </c>
-      <c r="BN25" s="83">
+      <c r="BN25" s="77">
         <v>0.53859999999999997</v>
       </c>
-      <c r="BO25" s="84">
+      <c r="BO25" s="78">
         <v>0.77400000000000002</v>
       </c>
     </row>
     <row r="26" spans="3:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB26" s="85">
+      <c r="BB26" s="79">
         <v>2.6</v>
       </c>
-      <c r="BC26" s="83">
+      <c r="BC26" s="77">
         <v>0.1336</v>
       </c>
-      <c r="BD26" s="83">
+      <c r="BD26" s="77">
         <v>0.16769999999999999</v>
       </c>
-      <c r="BE26" s="83">
+      <c r="BE26" s="77">
         <v>0.20480000000000001</v>
       </c>
-      <c r="BF26" s="83">
+      <c r="BF26" s="77">
         <v>0.2392</v>
       </c>
-      <c r="BG26" s="83">
+      <c r="BG26" s="77">
         <v>0.2727</v>
       </c>
-      <c r="BH26" s="83">
+      <c r="BH26" s="77">
         <v>0.2898</v>
       </c>
-      <c r="BI26" s="83">
+      <c r="BI26" s="77">
         <v>0.25659999999999999</v>
       </c>
-      <c r="BJ26" s="83">
+      <c r="BJ26" s="77">
         <v>0.2059</v>
       </c>
-      <c r="BK26" s="83">
+      <c r="BK26" s="77">
         <v>0.20039999999999999</v>
       </c>
-      <c r="BL26" s="83">
+      <c r="BL26" s="77">
         <v>0.24629999999999999</v>
       </c>
-      <c r="BM26" s="83">
+      <c r="BM26" s="77">
         <v>0.2555</v>
       </c>
-      <c r="BN26" s="83">
+      <c r="BN26" s="77">
         <v>0.50470000000000004</v>
       </c>
-      <c r="BO26" s="84">
+      <c r="BO26" s="78">
         <v>0.62309999999999999</v>
       </c>
     </row>
     <row r="27" spans="3:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB27" s="85">
+      <c r="BB27" s="79">
         <v>2.7</v>
       </c>
-      <c r="BC27" s="83">
+      <c r="BC27" s="77">
         <v>0.1328</v>
       </c>
-      <c r="BD27" s="83">
+      <c r="BD27" s="77">
         <v>0.16539999999999999</v>
       </c>
-      <c r="BE27" s="83">
+      <c r="BE27" s="77">
         <v>0.2039</v>
       </c>
-      <c r="BF27" s="83">
+      <c r="BF27" s="77">
         <v>0.24010000000000001</v>
       </c>
-      <c r="BG27" s="83">
+      <c r="BG27" s="77">
         <v>0.2757</v>
       </c>
-      <c r="BH27" s="83">
+      <c r="BH27" s="77">
         <v>0.29630000000000001</v>
       </c>
-      <c r="BI27" s="83">
+      <c r="BI27" s="77">
         <v>0.26619999999999999</v>
       </c>
-      <c r="BJ27" s="83">
+      <c r="BJ27" s="77">
         <v>0.2165</v>
       </c>
-      <c r="BK27" s="83">
+      <c r="BK27" s="77">
         <v>0.20150000000000001</v>
       </c>
-      <c r="BL27" s="83">
+      <c r="BL27" s="77">
         <v>0.25119999999999998</v>
       </c>
-      <c r="BM27" s="83">
+      <c r="BM27" s="77">
         <v>0.25040000000000001</v>
       </c>
-      <c r="BN27" s="83">
+      <c r="BN27" s="77">
         <v>0.46489999999999998</v>
       </c>
-      <c r="BO27" s="84">
+      <c r="BO27" s="78">
         <v>0.51839999999999997</v>
       </c>
     </row>
     <row r="28" spans="3:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB28" s="85">
+      <c r="BB28" s="79">
         <v>2.8</v>
       </c>
-      <c r="BC28" s="83">
+      <c r="BC28" s="77">
         <v>0.1323</v>
       </c>
-      <c r="BD28" s="83">
+      <c r="BD28" s="77">
         <v>0.16239999999999999</v>
       </c>
-      <c r="BE28" s="83">
+      <c r="BE28" s="77">
         <v>0.20230000000000001</v>
       </c>
-      <c r="BF28" s="83">
+      <c r="BF28" s="77">
         <v>0.2402</v>
       </c>
-      <c r="BG28" s="83">
+      <c r="BG28" s="77">
         <v>0.27789999999999998</v>
       </c>
-      <c r="BH28" s="83">
+      <c r="BH28" s="77">
         <v>0.3019</v>
       </c>
-      <c r="BI28" s="83">
+      <c r="BI28" s="77">
         <v>0.27650000000000002</v>
       </c>
-      <c r="BJ28" s="83">
+      <c r="BJ28" s="77">
         <v>0.22539999999999999</v>
       </c>
-      <c r="BK28" s="83">
+      <c r="BK28" s="77">
         <v>0.2001</v>
       </c>
-      <c r="BL28" s="83">
+      <c r="BL28" s="77">
         <v>0.25840000000000002</v>
       </c>
-      <c r="BM28" s="83">
+      <c r="BM28" s="77">
         <v>0.25040000000000001</v>
       </c>
-      <c r="BN28" s="83">
+      <c r="BN28" s="77">
         <v>0.42180000000000001</v>
       </c>
-      <c r="BO28" s="84">
+      <c r="BO28" s="78">
         <v>0.44450000000000001</v>
       </c>
     </row>
     <row r="29" spans="3:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB29" s="85">
+      <c r="BB29" s="79">
         <v>2.9</v>
       </c>
-      <c r="BC29" s="83">
+      <c r="BC29" s="77">
         <v>0.13339999999999999</v>
       </c>
-      <c r="BD29" s="83">
+      <c r="BD29" s="77">
         <v>0.15870000000000001</v>
       </c>
-      <c r="BE29" s="83">
+      <c r="BE29" s="77">
         <v>0.19989999999999999</v>
       </c>
-      <c r="BF29" s="83">
+      <c r="BF29" s="77">
         <v>0.2394</v>
       </c>
-      <c r="BG29" s="83">
+      <c r="BG29" s="77">
         <v>0.27910000000000001</v>
       </c>
-      <c r="BH29" s="83">
+      <c r="BH29" s="77">
         <v>0.30649999999999999</v>
       </c>
-      <c r="BI29" s="83">
+      <c r="BI29" s="77">
         <v>0.28610000000000002</v>
       </c>
-      <c r="BJ29" s="83">
+      <c r="BJ29" s="77">
         <v>0.2321</v>
       </c>
-      <c r="BK29" s="83">
+      <c r="BK29" s="77">
         <v>0.1953</v>
       </c>
-      <c r="BL29" s="83">
+      <c r="BL29" s="77">
         <v>0.2792</v>
       </c>
-      <c r="BM29" s="83">
+      <c r="BM29" s="77">
         <v>0.27139999999999997</v>
       </c>
-      <c r="BN29" s="83">
+      <c r="BN29" s="77">
         <v>0.3785</v>
       </c>
-      <c r="BO29" s="84">
+      <c r="BO29" s="78">
         <v>0.40050000000000002</v>
       </c>
     </row>
     <row r="30" spans="3:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB30" s="85">
+      <c r="BB30" s="79">
         <v>3</v>
       </c>
-      <c r="BC30" s="83">
+      <c r="BC30" s="77">
         <v>0.13519999999999999</v>
       </c>
-      <c r="BD30" s="83">
+      <c r="BD30" s="77">
         <v>0.1545</v>
       </c>
-      <c r="BE30" s="83">
+      <c r="BE30" s="77">
         <v>0.19670000000000001</v>
       </c>
-      <c r="BF30" s="83">
+      <c r="BF30" s="77">
         <v>0.23780000000000001</v>
       </c>
-      <c r="BG30" s="83">
+      <c r="BG30" s="77">
         <v>0.27910000000000001</v>
       </c>
-      <c r="BH30" s="83">
+      <c r="BH30" s="77">
         <v>0.30980000000000002</v>
       </c>
-      <c r="BI30" s="83">
+      <c r="BI30" s="77">
         <v>0.2944</v>
       </c>
-      <c r="BJ30" s="83">
+      <c r="BJ30" s="77">
         <v>0.2364</v>
       </c>
-      <c r="BK30" s="83">
+      <c r="BK30" s="77">
         <v>0.18679999999999999</v>
       </c>
-      <c r="BL30" s="83">
+      <c r="BL30" s="77">
         <v>0.31030000000000002</v>
       </c>
-      <c r="BM30" s="83">
+      <c r="BM30" s="77">
         <v>0.317</v>
       </c>
-      <c r="BN30" s="83">
+      <c r="BN30" s="77">
         <v>0.33679999999999999</v>
       </c>
-      <c r="BO30" s="84">
+      <c r="BO30" s="78">
         <v>0.38719999999999999</v>
       </c>
     </row>
     <row r="31" spans="3:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB31" s="85">
+      <c r="BB31" s="79">
         <v>3.1</v>
       </c>
-      <c r="BC31" s="83">
+      <c r="BC31" s="77">
         <v>0.13730000000000001</v>
       </c>
-      <c r="BD31" s="83">
+      <c r="BD31" s="77">
         <v>0.14960000000000001</v>
       </c>
-      <c r="BE31" s="83">
+      <c r="BE31" s="77">
         <v>0.19270000000000001</v>
       </c>
-      <c r="BF31" s="83">
+      <c r="BF31" s="77">
         <v>0.23519999999999999</v>
       </c>
-      <c r="BG31" s="83">
+      <c r="BG31" s="77">
         <v>0.27789999999999998</v>
       </c>
-      <c r="BH31" s="83">
+      <c r="BH31" s="77">
         <v>0.31180000000000002</v>
       </c>
-      <c r="BI31" s="83">
+      <c r="BI31" s="77">
         <v>0.3009</v>
       </c>
-      <c r="BJ31" s="83">
+      <c r="BJ31" s="77">
         <v>0.23849999999999999</v>
       </c>
-      <c r="BK31" s="83">
+      <c r="BK31" s="77">
         <v>0.17299999999999999</v>
       </c>
-      <c r="BL31" s="83">
+      <c r="BL31" s="77">
         <v>0.34710000000000002</v>
       </c>
-      <c r="BM31" s="83">
+      <c r="BM31" s="77">
         <v>0.37990000000000002</v>
       </c>
-      <c r="BN31" s="83">
+      <c r="BN31" s="77">
         <v>0.29859999999999998</v>
       </c>
-      <c r="BO31" s="84">
+      <c r="BO31" s="78">
         <v>0.39910000000000001</v>
       </c>
     </row>
     <row r="32" spans="3:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB32" s="85">
+      <c r="BB32" s="79">
         <v>3.2</v>
       </c>
-      <c r="BC32" s="83">
+      <c r="BC32" s="77">
         <v>0.13950000000000001</v>
       </c>
-      <c r="BD32" s="83">
+      <c r="BD32" s="77">
         <v>0.14419999999999999</v>
       </c>
-      <c r="BE32" s="83">
+      <c r="BE32" s="77">
         <v>0.188</v>
       </c>
-      <c r="BF32" s="83">
+      <c r="BF32" s="77">
         <v>0.23169999999999999</v>
       </c>
-      <c r="BG32" s="83">
+      <c r="BG32" s="77">
         <v>0.27539999999999998</v>
       </c>
-      <c r="BH32" s="83">
+      <c r="BH32" s="77">
         <v>0.31219999999999998</v>
       </c>
-      <c r="BI32" s="83">
+      <c r="BI32" s="77">
         <v>0.30530000000000002</v>
       </c>
-      <c r="BJ32" s="83">
+      <c r="BJ32" s="77">
         <v>0.23899999999999999</v>
       </c>
-      <c r="BK32" s="83">
+      <c r="BK32" s="77">
         <v>0.1537</v>
       </c>
-      <c r="BL32" s="83">
+      <c r="BL32" s="77">
         <v>0.38540000000000002</v>
       </c>
-      <c r="BM32" s="83">
+      <c r="BM32" s="77">
         <v>0.45579999999999998</v>
       </c>
-      <c r="BN32" s="83">
+      <c r="BN32" s="77">
         <v>0.26860000000000001</v>
       </c>
-      <c r="BO32" s="84">
+      <c r="BO32" s="78">
         <v>0.4259</v>
       </c>
     </row>
     <row r="33" spans="54:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB33" s="85">
+      <c r="BB33" s="79">
         <v>3.3</v>
       </c>
-      <c r="BC33" s="83">
+      <c r="BC33" s="77">
         <v>0.14149999999999999</v>
       </c>
-      <c r="BD33" s="83">
+      <c r="BD33" s="77">
         <v>0.14069999999999999</v>
       </c>
-      <c r="BE33" s="83">
+      <c r="BE33" s="77">
         <v>0.18279999999999999</v>
       </c>
-      <c r="BF33" s="83">
+      <c r="BF33" s="77">
         <v>0.22750000000000001</v>
       </c>
-      <c r="BG33" s="83">
+      <c r="BG33" s="77">
         <v>0.2717</v>
       </c>
-      <c r="BH33" s="83">
+      <c r="BH33" s="77">
         <v>0.311</v>
       </c>
-      <c r="BI33" s="83">
+      <c r="BI33" s="77">
         <v>0.30790000000000001</v>
       </c>
-      <c r="BJ33" s="83">
+      <c r="BJ33" s="77">
         <v>0.23910000000000001</v>
       </c>
-      <c r="BK33" s="83">
+      <c r="BK33" s="77">
         <v>0.15049999999999999</v>
       </c>
-      <c r="BL33" s="83">
+      <c r="BL33" s="77">
         <v>0.4229</v>
       </c>
-      <c r="BM33" s="83">
+      <c r="BM33" s="77">
         <v>0.53990000000000005</v>
       </c>
-      <c r="BN33" s="83">
+      <c r="BN33" s="77">
         <v>0.25459999999999999</v>
       </c>
-      <c r="BO33" s="84">
+      <c r="BO33" s="78">
         <v>0.45879999999999999</v>
       </c>
     </row>
     <row r="34" spans="54:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB34" s="85">
+      <c r="BB34" s="79">
         <v>3.4</v>
       </c>
-      <c r="BC34" s="83">
+      <c r="BC34" s="77">
         <v>0.1434</v>
       </c>
-      <c r="BD34" s="83">
+      <c r="BD34" s="77">
         <v>0.1411</v>
       </c>
-      <c r="BE34" s="83">
+      <c r="BE34" s="77">
         <v>0.1772</v>
       </c>
-      <c r="BF34" s="83">
+      <c r="BF34" s="77">
         <v>0.22270000000000001</v>
       </c>
-      <c r="BG34" s="83">
+      <c r="BG34" s="77">
         <v>0.26690000000000003</v>
       </c>
-      <c r="BH34" s="83">
+      <c r="BH34" s="77">
         <v>0.30840000000000001</v>
       </c>
-      <c r="BI34" s="83">
+      <c r="BI34" s="77">
         <v>0.30890000000000001</v>
       </c>
-      <c r="BJ34" s="83">
+      <c r="BJ34" s="77">
         <v>0.23980000000000001</v>
       </c>
-      <c r="BK34" s="83">
+      <c r="BK34" s="77">
         <v>0.156</v>
       </c>
-      <c r="BL34" s="83">
+      <c r="BL34" s="77">
         <v>0.4577</v>
       </c>
-      <c r="BM34" s="83">
+      <c r="BM34" s="77">
         <v>0.62809999999999999</v>
       </c>
-      <c r="BN34" s="83">
+      <c r="BN34" s="77">
         <v>0.27410000000000001</v>
       </c>
-      <c r="BO34" s="84">
+      <c r="BO34" s="78">
         <v>0.49249999999999999</v>
       </c>
     </row>
     <row r="35" spans="54:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB35" s="85">
+      <c r="BB35" s="79">
         <v>3.5</v>
       </c>
-      <c r="BC35" s="83">
+      <c r="BC35" s="77">
         <v>0.1449</v>
       </c>
-      <c r="BD35" s="83">
+      <c r="BD35" s="77">
         <v>0.14299999999999999</v>
       </c>
-      <c r="BE35" s="83">
+      <c r="BE35" s="77">
         <v>0.17199999999999999</v>
       </c>
-      <c r="BF35" s="83">
+      <c r="BF35" s="77">
         <v>0.21759999999999999</v>
       </c>
-      <c r="BG35" s="83">
+      <c r="BG35" s="77">
         <v>0.26129999999999998</v>
       </c>
-      <c r="BH35" s="83">
+      <c r="BH35" s="77">
         <v>0.3044</v>
       </c>
-      <c r="BI35" s="83">
+      <c r="BI35" s="77">
         <v>0.3085</v>
       </c>
-      <c r="BJ35" s="83">
+      <c r="BJ35" s="77">
         <v>0.24129999999999999</v>
       </c>
-      <c r="BK35" s="83">
+      <c r="BK35" s="77">
         <v>0.16170000000000001</v>
       </c>
-      <c r="BL35" s="83">
+      <c r="BL35" s="77">
         <v>0.48830000000000001</v>
       </c>
-      <c r="BM35" s="83">
+      <c r="BM35" s="77">
         <v>0.71789999999999998</v>
       </c>
-      <c r="BN35" s="83">
+      <c r="BN35" s="77">
         <v>0.33200000000000002</v>
       </c>
-      <c r="BO35" s="84">
+      <c r="BO35" s="78">
         <v>0.52400000000000002</v>
       </c>
     </row>
     <row r="36" spans="54:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB36" s="85">
+      <c r="BB36" s="79">
         <v>3.6</v>
       </c>
-      <c r="BC36" s="83">
+      <c r="BC36" s="77">
         <v>0.14599999999999999</v>
       </c>
-      <c r="BD36" s="83">
+      <c r="BD36" s="77">
         <v>0.1459</v>
       </c>
-      <c r="BE36" s="83">
+      <c r="BE36" s="77">
         <v>0.17169999999999999</v>
       </c>
-      <c r="BF36" s="83">
+      <c r="BF36" s="77">
         <v>0.21279999999999999</v>
       </c>
-      <c r="BG36" s="83">
+      <c r="BG36" s="77">
         <v>0.25509999999999999</v>
       </c>
-      <c r="BH36" s="83">
+      <c r="BH36" s="77">
         <v>0.29920000000000002</v>
       </c>
-      <c r="BI36" s="83">
+      <c r="BI36" s="77">
         <v>0.30719999999999997</v>
       </c>
-      <c r="BJ36" s="83">
+      <c r="BJ36" s="77">
         <v>0.2437</v>
       </c>
-      <c r="BK36" s="83">
+      <c r="BK36" s="77">
         <v>0.17510000000000001</v>
       </c>
-      <c r="BL36" s="83">
+      <c r="BL36" s="77">
         <v>0.51349999999999996</v>
       </c>
-      <c r="BM36" s="83">
+      <c r="BM36" s="77">
         <v>0.80720000000000003</v>
       </c>
-      <c r="BN36" s="83">
+      <c r="BN36" s="77">
         <v>0.39960000000000001</v>
       </c>
-      <c r="BO36" s="84">
+      <c r="BO36" s="78">
         <v>0.55159999999999998</v>
       </c>
     </row>
     <row r="37" spans="54:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB37" s="85">
+      <c r="BB37" s="79">
         <v>3.7</v>
       </c>
-      <c r="BC37" s="83">
+      <c r="BC37" s="77">
         <v>0.14680000000000001</v>
       </c>
-      <c r="BD37" s="83">
+      <c r="BD37" s="77">
         <v>0.14929999999999999</v>
       </c>
-      <c r="BE37" s="83">
+      <c r="BE37" s="77">
         <v>0.1736</v>
       </c>
-      <c r="BF37" s="83">
+      <c r="BF37" s="77">
         <v>0.2087</v>
       </c>
-      <c r="BG37" s="83">
+      <c r="BG37" s="77">
         <v>0.24879999999999999</v>
       </c>
-      <c r="BH37" s="83">
+      <c r="BH37" s="77">
         <v>0.29320000000000002</v>
       </c>
-      <c r="BI37" s="83">
+      <c r="BI37" s="77">
         <v>0.30530000000000002</v>
       </c>
-      <c r="BJ37" s="83">
+      <c r="BJ37" s="77">
         <v>0.24660000000000001</v>
       </c>
-      <c r="BK37" s="83">
+      <c r="BK37" s="77">
         <v>0.2044</v>
       </c>
-      <c r="BL37" s="83">
+      <c r="BL37" s="77">
         <v>0.5323</v>
       </c>
-      <c r="BM37" s="83">
+      <c r="BM37" s="77">
         <v>0.89390000000000003</v>
       </c>
-      <c r="BN37" s="83">
+      <c r="BN37" s="77">
         <v>0.47260000000000002</v>
       </c>
-      <c r="BO37" s="84">
+      <c r="BO37" s="78">
         <v>0.57399999999999995</v>
       </c>
     </row>
     <row r="38" spans="54:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB38" s="85">
+      <c r="BB38" s="79">
         <v>3.8</v>
       </c>
-      <c r="BC38" s="83">
+      <c r="BC38" s="77">
         <v>0.1474</v>
       </c>
-      <c r="BD38" s="83">
+      <c r="BD38" s="77">
         <v>0.153</v>
       </c>
-      <c r="BE38" s="83">
+      <c r="BE38" s="77">
         <v>0.1762</v>
       </c>
-      <c r="BF38" s="83">
+      <c r="BF38" s="77">
         <v>0.20599999999999999</v>
       </c>
-      <c r="BG38" s="83">
+      <c r="BG38" s="77">
         <v>0.2429</v>
       </c>
-      <c r="BH38" s="83">
+      <c r="BH38" s="77">
         <v>0.28660000000000002</v>
       </c>
-      <c r="BI38" s="83">
+      <c r="BI38" s="77">
         <v>0.3029</v>
       </c>
-      <c r="BJ38" s="83">
+      <c r="BJ38" s="77">
         <v>0.24959999999999999</v>
       </c>
-      <c r="BK38" s="83">
+      <c r="BK38" s="77">
         <v>0.2414</v>
       </c>
-      <c r="BL38" s="83">
+      <c r="BL38" s="77">
         <v>0.54390000000000005</v>
       </c>
-      <c r="BM38" s="83">
+      <c r="BM38" s="77">
         <v>0.97650000000000003</v>
       </c>
-      <c r="BN38" s="83">
+      <c r="BN38" s="77">
         <v>0.55010000000000003</v>
       </c>
-      <c r="BO38" s="84">
+      <c r="BO38" s="78">
         <v>0.59040000000000004</v>
       </c>
     </row>
     <row r="39" spans="54:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB39" s="85">
+      <c r="BB39" s="79">
         <v>3.9</v>
       </c>
-      <c r="BC39" s="83">
+      <c r="BC39" s="77">
         <v>0.14810000000000001</v>
       </c>
-      <c r="BD39" s="83">
+      <c r="BD39" s="77">
         <v>0.157</v>
       </c>
-      <c r="BE39" s="83">
+      <c r="BE39" s="77">
         <v>0.1789</v>
       </c>
-      <c r="BF39" s="83">
+      <c r="BF39" s="77">
         <v>0.20660000000000001</v>
       </c>
-      <c r="BG39" s="83">
+      <c r="BG39" s="77">
         <v>0.2379</v>
       </c>
-      <c r="BH39" s="83">
+      <c r="BH39" s="77">
         <v>0.27989999999999998</v>
       </c>
-      <c r="BI39" s="83">
+      <c r="BI39" s="77">
         <v>0.29970000000000002</v>
       </c>
-      <c r="BJ39" s="83">
+      <c r="BJ39" s="77">
         <v>0.25559999999999999</v>
       </c>
-      <c r="BK39" s="83">
+      <c r="BK39" s="77">
         <v>0.28120000000000001</v>
       </c>
-      <c r="BL39" s="83">
+      <c r="BL39" s="77">
         <v>0.54769999999999996</v>
       </c>
-      <c r="BM39" s="83">
+      <c r="BM39" s="77">
         <v>1.0531999999999999</v>
       </c>
-      <c r="BN39" s="83">
+      <c r="BN39" s="77">
         <v>0.63149999999999995</v>
       </c>
-      <c r="BO39" s="84">
+      <c r="BO39" s="78">
         <v>0.60009999999999997</v>
       </c>
     </row>
     <row r="40" spans="54:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB40" s="85">
+      <c r="BB40" s="79">
         <v>4</v>
       </c>
-      <c r="BC40" s="83">
+      <c r="BC40" s="77">
         <v>0.1492</v>
       </c>
-      <c r="BD40" s="83">
+      <c r="BD40" s="77">
         <v>0.1615</v>
       </c>
-      <c r="BE40" s="83">
+      <c r="BE40" s="77">
         <v>0.18210000000000001</v>
       </c>
-      <c r="BF40" s="83">
+      <c r="BF40" s="77">
         <v>0.20960000000000001</v>
       </c>
-      <c r="BG40" s="83">
+      <c r="BG40" s="77">
         <v>0.23449999999999999</v>
       </c>
-      <c r="BH40" s="83">
+      <c r="BH40" s="77">
         <v>0.27339999999999998</v>
       </c>
-      <c r="BI40" s="83">
+      <c r="BI40" s="77">
         <v>0.29599999999999999</v>
       </c>
-      <c r="BJ40" s="83">
+      <c r="BJ40" s="77">
         <v>0.27229999999999999</v>
       </c>
-      <c r="BK40" s="83">
+      <c r="BK40" s="77">
         <v>0.31950000000000001</v>
       </c>
-      <c r="BL40" s="83">
+      <c r="BL40" s="77">
         <v>0.54300000000000004</v>
       </c>
-      <c r="BM40" s="83">
+      <c r="BM40" s="77">
         <v>1.1224000000000001</v>
       </c>
-      <c r="BN40" s="83">
+      <c r="BN40" s="77">
         <v>0.71530000000000005</v>
       </c>
-      <c r="BO40" s="84">
+      <c r="BO40" s="78">
         <v>0.6028</v>
       </c>
     </row>
     <row r="41" spans="54:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB41" s="85">
+      <c r="BB41" s="79">
         <v>4.0999999999999996</v>
       </c>
-      <c r="BC41" s="83">
+      <c r="BC41" s="77">
         <v>0.15110000000000001</v>
       </c>
-      <c r="BD41" s="83">
+      <c r="BD41" s="77">
         <v>0.1668</v>
       </c>
-      <c r="BE41" s="83">
+      <c r="BE41" s="77">
         <v>0.1865</v>
       </c>
-      <c r="BF41" s="83">
+      <c r="BF41" s="77">
         <v>0.21560000000000001</v>
       </c>
-      <c r="BG41" s="83">
+      <c r="BG41" s="77">
         <v>0.23330000000000001</v>
       </c>
-      <c r="BH41" s="83">
+      <c r="BH41" s="77">
         <v>0.26750000000000002</v>
       </c>
-      <c r="BI41" s="83">
+      <c r="BI41" s="77">
         <v>0.29189999999999999</v>
       </c>
-      <c r="BJ41" s="83">
+      <c r="BJ41" s="77">
         <v>0.29020000000000001</v>
       </c>
-      <c r="BK41" s="83">
+      <c r="BK41" s="77">
         <v>0.35239999999999999</v>
       </c>
-      <c r="BL41" s="83">
+      <c r="BL41" s="77">
         <v>0.52900000000000003</v>
       </c>
-      <c r="BM41" s="83">
+      <c r="BM41" s="77">
         <v>1.1822999999999999</v>
       </c>
-      <c r="BN41" s="83">
+      <c r="BN41" s="77">
         <v>0.80069999999999997</v>
       </c>
-      <c r="BO41" s="84">
+      <c r="BO41" s="78">
         <v>0.5978</v>
       </c>
     </row>
     <row r="42" spans="54:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB42" s="85">
+      <c r="BB42" s="79">
         <v>4.2</v>
       </c>
-      <c r="BC42" s="83">
+      <c r="BC42" s="77">
         <v>0.15459999999999999</v>
       </c>
-      <c r="BD42" s="83">
+      <c r="BD42" s="77">
         <v>0.1734</v>
       </c>
-      <c r="BE42" s="83">
+      <c r="BE42" s="77">
         <v>0.1946</v>
       </c>
-      <c r="BF42" s="83">
+      <c r="BF42" s="77">
         <v>0.22789999999999999</v>
       </c>
-      <c r="BG42" s="83">
+      <c r="BG42" s="77">
         <v>0.23499999999999999</v>
       </c>
-      <c r="BH42" s="83">
+      <c r="BH42" s="77">
         <v>0.26250000000000001</v>
       </c>
-      <c r="BI42" s="83">
+      <c r="BI42" s="77">
         <v>0.28749999999999998</v>
       </c>
-      <c r="BJ42" s="83">
+      <c r="BJ42" s="77">
         <v>0.30549999999999999</v>
       </c>
-      <c r="BK42" s="83">
+      <c r="BK42" s="77">
         <v>0.37690000000000001</v>
       </c>
-      <c r="BL42" s="83">
+      <c r="BL42" s="77">
         <v>0.50509999999999999</v>
       </c>
-      <c r="BM42" s="83">
+      <c r="BM42" s="77">
         <v>1.2309000000000001</v>
       </c>
-      <c r="BN42" s="83">
+      <c r="BN42" s="77">
         <v>0.8881</v>
       </c>
-      <c r="BO42" s="84">
+      <c r="BO42" s="78">
         <v>0.58460000000000001</v>
       </c>
     </row>
     <row r="43" spans="54:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB43" s="85">
+      <c r="BB43" s="79">
         <v>4.3</v>
       </c>
-      <c r="BC43" s="83">
+      <c r="BC43" s="77">
         <v>0.16089999999999999</v>
       </c>
-      <c r="BD43" s="83">
+      <c r="BD43" s="77">
         <v>0.18190000000000001</v>
       </c>
-      <c r="BE43" s="83">
+      <c r="BE43" s="77">
         <v>0.2135</v>
       </c>
-      <c r="BF43" s="83">
+      <c r="BF43" s="77">
         <v>0.2465</v>
       </c>
-      <c r="BG43" s="83">
+      <c r="BG43" s="77">
         <v>0.24010000000000001</v>
       </c>
-      <c r="BH43" s="83">
+      <c r="BH43" s="77">
         <v>0.2586</v>
       </c>
-      <c r="BI43" s="83">
+      <c r="BI43" s="77">
         <v>0.28270000000000001</v>
       </c>
-      <c r="BJ43" s="83">
+      <c r="BJ43" s="77">
         <v>0.316</v>
       </c>
-      <c r="BK43" s="83">
+      <c r="BK43" s="77">
         <v>0.39119999999999999</v>
       </c>
-      <c r="BL43" s="83">
+      <c r="BL43" s="77">
         <v>0.4703</v>
       </c>
-      <c r="BM43" s="83">
+      <c r="BM43" s="77">
         <v>1.2662</v>
       </c>
-      <c r="BN43" s="83">
+      <c r="BN43" s="77">
         <v>0.97850000000000004</v>
       </c>
-      <c r="BO43" s="84">
+      <c r="BO43" s="78">
         <v>0.56340000000000001</v>
       </c>
     </row>
     <row r="44" spans="54:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB44" s="85">
+      <c r="BB44" s="79">
         <v>4.4000000000000004</v>
       </c>
-      <c r="BC44" s="83">
+      <c r="BC44" s="77">
         <v>0.16980000000000001</v>
       </c>
-      <c r="BD44" s="83">
+      <c r="BD44" s="77">
         <v>0.1928</v>
       </c>
-      <c r="BE44" s="83">
+      <c r="BE44" s="77">
         <v>0.24560000000000001</v>
       </c>
-      <c r="BF44" s="83">
+      <c r="BF44" s="77">
         <v>0.27250000000000002</v>
       </c>
-      <c r="BG44" s="83">
+      <c r="BG44" s="77">
         <v>0.24909999999999999</v>
       </c>
-      <c r="BH44" s="83">
+      <c r="BH44" s="77">
         <v>0.25609999999999999</v>
       </c>
-      <c r="BI44" s="83">
+      <c r="BI44" s="77">
         <v>0.27760000000000001</v>
       </c>
-      <c r="BJ44" s="83">
+      <c r="BJ44" s="77">
         <v>0.3206</v>
       </c>
-      <c r="BK44" s="83">
+      <c r="BK44" s="77">
         <v>0.39489999999999997</v>
       </c>
-      <c r="BL44" s="83">
+      <c r="BL44" s="77">
         <v>0.42430000000000001</v>
       </c>
-      <c r="BM44" s="83">
+      <c r="BM44" s="77">
         <v>1.2862</v>
       </c>
-      <c r="BN44" s="83">
+      <c r="BN44" s="77">
         <v>1.0732999999999999</v>
       </c>
-      <c r="BO44" s="84">
+      <c r="BO44" s="78">
         <v>0.53500000000000003</v>
       </c>
     </row>
     <row r="45" spans="54:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB45" s="85">
+      <c r="BB45" s="79">
         <v>4.5</v>
       </c>
-      <c r="BC45" s="83">
+      <c r="BC45" s="77">
         <v>0.17929999999999999</v>
       </c>
-      <c r="BD45" s="83">
+      <c r="BD45" s="77">
         <v>0.2069</v>
       </c>
-      <c r="BE45" s="83">
+      <c r="BE45" s="77">
         <v>0.28799999999999998</v>
       </c>
-      <c r="BF45" s="83">
+      <c r="BF45" s="77">
         <v>0.30649999999999999</v>
       </c>
-      <c r="BG45" s="83">
+      <c r="BG45" s="77">
         <v>0.26240000000000002</v>
       </c>
-      <c r="BH45" s="83">
+      <c r="BH45" s="77">
         <v>0.255</v>
       </c>
-      <c r="BI45" s="83">
+      <c r="BI45" s="77">
         <v>0.27189999999999998</v>
       </c>
-      <c r="BJ45" s="83">
+      <c r="BJ45" s="77">
         <v>0.31900000000000001</v>
       </c>
-      <c r="BK45" s="83">
+      <c r="BK45" s="77">
         <v>0.3891</v>
       </c>
-      <c r="BL45" s="83">
+      <c r="BL45" s="77">
         <v>0.36770000000000003</v>
       </c>
-      <c r="BM45" s="83">
+      <c r="BM45" s="77">
         <v>1.2894000000000001</v>
       </c>
-      <c r="BN45" s="83">
+      <c r="BN45" s="77">
         <v>1.1733</v>
       </c>
-      <c r="BO45" s="84">
+      <c r="BO45" s="78">
         <v>0.50139999999999996</v>
       </c>
     </row>
     <row r="46" spans="54:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB46" s="85">
+      <c r="BB46" s="79">
         <v>4.5999999999999996</v>
       </c>
-      <c r="BC46" s="83">
+      <c r="BC46" s="77">
         <v>0.18940000000000001</v>
       </c>
-      <c r="BD46" s="83">
+      <c r="BD46" s="77">
         <v>0.22509999999999999</v>
       </c>
-      <c r="BE46" s="83">
+      <c r="BE46" s="77">
         <v>0.34200000000000003</v>
       </c>
-      <c r="BF46" s="83">
+      <c r="BF46" s="77">
         <v>0.34939999999999999</v>
       </c>
-      <c r="BG46" s="83">
+      <c r="BG46" s="77">
         <v>0.28000000000000003</v>
       </c>
-      <c r="BH46" s="83">
+      <c r="BH46" s="77">
         <v>0.25509999999999999</v>
       </c>
-      <c r="BI46" s="83">
+      <c r="BI46" s="77">
         <v>0.26540000000000002</v>
       </c>
-      <c r="BJ46" s="83">
+      <c r="BJ46" s="77">
         <v>0.31219999999999998</v>
       </c>
-      <c r="BK46" s="83">
+      <c r="BK46" s="77">
         <v>0.37619999999999998</v>
       </c>
-      <c r="BL46" s="83">
+      <c r="BL46" s="77">
         <v>0.30159999999999998</v>
       </c>
-      <c r="BM46" s="83">
+      <c r="BM46" s="77">
         <v>1.2746999999999999</v>
       </c>
-      <c r="BN46" s="83">
+      <c r="BN46" s="77">
         <v>1.2786</v>
       </c>
-      <c r="BO46" s="84">
+      <c r="BO46" s="78">
         <v>0.46739999999999998</v>
       </c>
     </row>
     <row r="47" spans="54:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB47" s="85">
+      <c r="BB47" s="79">
         <v>4.7</v>
       </c>
-      <c r="BC47" s="83">
+      <c r="BC47" s="77">
         <v>0.2</v>
       </c>
-      <c r="BD47" s="83">
+      <c r="BD47" s="77">
         <v>0.2495</v>
       </c>
-      <c r="BE47" s="83">
+      <c r="BE47" s="77">
         <v>0.4083</v>
       </c>
-      <c r="BF47" s="83">
+      <c r="BF47" s="77">
         <v>0.40129999999999999</v>
       </c>
-      <c r="BG47" s="83">
+      <c r="BG47" s="77">
         <v>0.30209999999999998</v>
       </c>
-      <c r="BH47" s="83">
+      <c r="BH47" s="77">
         <v>0.25629999999999997</v>
       </c>
-      <c r="BI47" s="83">
+      <c r="BI47" s="77">
         <v>0.25779999999999997</v>
       </c>
-      <c r="BJ47" s="83">
+      <c r="BJ47" s="77">
         <v>0.30099999999999999</v>
       </c>
-      <c r="BK47" s="83">
+      <c r="BK47" s="77">
         <v>0.35880000000000001</v>
       </c>
-      <c r="BL47" s="83">
+      <c r="BL47" s="77">
         <v>0.2288</v>
       </c>
-      <c r="BM47" s="83">
+      <c r="BM47" s="77">
         <v>1.2421</v>
       </c>
-      <c r="BN47" s="83">
+      <c r="BN47" s="77">
         <v>1.389</v>
       </c>
-      <c r="BO47" s="84">
+      <c r="BO47" s="78">
         <v>0.44290000000000002</v>
       </c>
     </row>
     <row r="48" spans="54:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB48" s="85">
+      <c r="BB48" s="79">
         <v>4.8</v>
       </c>
-      <c r="BC48" s="83">
+      <c r="BC48" s="77">
         <v>0.21099999999999999</v>
       </c>
-      <c r="BD48" s="83">
+      <c r="BD48" s="77">
         <v>0.28639999999999999</v>
       </c>
-      <c r="BE48" s="83">
+      <c r="BE48" s="77">
         <v>0.48749999999999999</v>
       </c>
-      <c r="BF48" s="83">
+      <c r="BF48" s="77">
         <v>0.46200000000000002</v>
       </c>
-      <c r="BG48" s="83">
+      <c r="BG48" s="77">
         <v>0.32819999999999999</v>
       </c>
-      <c r="BH48" s="83">
+      <c r="BH48" s="77">
         <v>0.25819999999999999</v>
       </c>
-      <c r="BI48" s="83">
+      <c r="BI48" s="77">
         <v>0.2487</v>
       </c>
-      <c r="BJ48" s="83">
+      <c r="BJ48" s="77">
         <v>0.2868</v>
       </c>
-      <c r="BK48" s="83">
+      <c r="BK48" s="77">
         <v>0.3407</v>
       </c>
-      <c r="BL48" s="83">
+      <c r="BL48" s="77">
         <v>0.15390000000000001</v>
       </c>
-      <c r="BM48" s="83">
+      <c r="BM48" s="77">
         <v>1.1930000000000001</v>
       </c>
-      <c r="BN48" s="83">
+      <c r="BN48" s="77">
         <v>1.5033000000000001</v>
       </c>
-      <c r="BO48" s="84">
+      <c r="BO48" s="78">
         <v>0.44879999999999998</v>
       </c>
     </row>
     <row r="49" spans="54:67" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="BB49" s="85">
+      <c r="BB49" s="79">
         <v>4.9000000000000004</v>
       </c>
-      <c r="BC49" s="83">
+      <c r="BC49" s="77">
         <v>0.2225</v>
       </c>
-      <c r="BD49" s="83">
+      <c r="BD49" s="77">
         <v>0.34370000000000001</v>
       </c>
-      <c r="BE49" s="83">
+      <c r="BE49" s="77">
         <v>0.57920000000000005</v>
       </c>
-      <c r="BF49" s="83">
+      <c r="BF49" s="77">
         <v>0.53080000000000005</v>
       </c>
-      <c r="BG49" s="83">
+      <c r="BG49" s="77">
         <v>0.35799999999999998</v>
       </c>
-      <c r="BH49" s="83">
+      <c r="BH49" s="77">
         <v>0.26050000000000001</v>
       </c>
-      <c r="BI49" s="83">
+      <c r="BI49" s="77">
         <v>0.23780000000000001</v>
       </c>
-      <c r="BJ49" s="83">
+      <c r="BJ49" s="77">
         <v>0.2712</v>
       </c>
-      <c r="BK49" s="83">
+      <c r="BK49" s="77">
         <v>0.32429999999999998</v>
       </c>
-      <c r="BL49" s="83">
+      <c r="BL49" s="77">
         <v>9.3200000000000005E-2</v>
       </c>
-      <c r="BM49" s="83">
+      <c r="BM49" s="77">
         <v>1.1304000000000001</v>
       </c>
-      <c r="BN49" s="83">
+      <c r="BN49" s="77">
         <v>1.6194</v>
       </c>
-      <c r="BO49" s="84">
+      <c r="BO49" s="78">
         <v>0.52459999999999996</v>
       </c>
     </row>
     <row r="50" spans="54:67" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="BB50" s="86">
+      <c r="BB50" s="80">
         <v>5</v>
       </c>
-      <c r="BC50" s="87">
+      <c r="BC50" s="81">
         <v>0.2349</v>
       </c>
-      <c r="BD50" s="87">
+      <c r="BD50" s="81">
         <v>0.4128</v>
       </c>
-      <c r="BE50" s="87">
+      <c r="BE50" s="81">
         <v>0.68189999999999995</v>
       </c>
-      <c r="BF50" s="87">
+      <c r="BF50" s="81">
         <v>0.60629999999999995</v>
       </c>
-      <c r="BG50" s="87">
+      <c r="BG50" s="81">
         <v>0.3906</v>
       </c>
-      <c r="BH50" s="87">
+      <c r="BH50" s="81">
         <v>0.2626</v>
       </c>
-      <c r="BI50" s="87">
+      <c r="BI50" s="81">
         <v>0.2261</v>
       </c>
-      <c r="BJ50" s="87">
+      <c r="BJ50" s="81">
         <v>0.25519999999999998</v>
       </c>
-      <c r="BK50" s="87">
+      <c r="BK50" s="81">
         <v>0.31180000000000002</v>
       </c>
-      <c r="BL50" s="87">
+      <c r="BL50" s="81">
         <v>0.1157</v>
       </c>
-      <c r="BM50" s="87">
+      <c r="BM50" s="81">
         <v>1.0588</v>
       </c>
-      <c r="BN50" s="87">
+      <c r="BN50" s="81">
         <v>1.7345999999999999</v>
       </c>
-      <c r="BO50" s="88">
+      <c r="BO50" s="82">
         <v>0.65490000000000004</v>
       </c>
     </row>
@@ -33731,13 +33731,13 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G17">
         <f>AVERAGEIF(C3:AY15, "&lt;=200")</f>
@@ -33746,10 +33746,10 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G18">
         <f>MEDIAN(C3:AY15)</f>
@@ -33758,7 +33758,7 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F19" t="s">
         <v>5</v>
@@ -33770,7 +33770,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="F20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G20">
         <f>COUNTIF(C3:AY15, "&lt;=200") / (COUNT(C3:AY15) + COUNTIF(C3:AY15, "NaN")) * 100</f>
@@ -35935,7 +35935,7 @@
     </row>
     <row r="17" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I17">
         <f>AVERAGEIF(E3:BA15, "&lt;=200")</f>
@@ -35944,7 +35944,7 @@
     </row>
     <row r="18" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I18">
         <f>MEDIAN(E3:BA15)</f>
@@ -35962,7 +35962,7 @@
     </row>
     <row r="20" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I20">
         <f>COUNTIF(E3:BA15, "&lt;=200") / (COUNT(E3:BA15) + COUNTIF(E3:BA15, "NaN")) * 100</f>
@@ -36003,7 +36003,9 @@
   <dimension ref="B1:AY20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="51" width="5.88671875" customWidth="1"/>
+    <col min="3" max="7" width="5.88671875" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" customWidth="1"/>
+    <col min="9" max="51" width="5.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -36164,46 +36166,46 @@
         <v>0.7</v>
       </c>
       <c r="C3" s="1">
-        <v>0.41610000000000003</v>
+        <v>0.51900000000000002</v>
       </c>
       <c r="D3" s="1">
-        <v>0.17780000000000001</v>
+        <v>7.7200000000000005E-2</v>
       </c>
       <c r="E3" s="1">
-        <v>0.2036</v>
+        <v>0.3291</v>
       </c>
       <c r="F3" s="1">
-        <v>0.151</v>
+        <v>0.24490000000000001</v>
       </c>
       <c r="G3" s="1">
-        <v>0.24540000000000001</v>
+        <v>0.30280000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>0.14560000000000001</v>
+        <v>0.188</v>
       </c>
       <c r="I3" s="1">
-        <v>0.1618</v>
+        <v>0.18770000000000001</v>
       </c>
       <c r="J3" s="1">
-        <v>0.17230000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="K3" s="1">
-        <v>0.2009</v>
+        <v>0.28570000000000001</v>
       </c>
       <c r="L3" s="1">
-        <v>0.22470000000000001</v>
+        <v>0.33900000000000002</v>
       </c>
       <c r="M3" s="1">
-        <v>0.28179999999999999</v>
+        <v>0.40150000000000002</v>
       </c>
       <c r="N3" s="1">
-        <v>0.34870000000000001</v>
+        <v>0.43049999999999999</v>
       </c>
       <c r="O3" s="1">
-        <v>0.38350000000000001</v>
-      </c>
-      <c r="P3" s="1">
-        <v>0.3972</v>
+        <v>0.51980000000000004</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="Q3" s="1" t="s">
         <v>10</v>
@@ -36316,79 +36318,79 @@
         <v>0.8</v>
       </c>
       <c r="C4" s="1">
-        <v>0.75290000000000001</v>
+        <v>1.2056</v>
       </c>
       <c r="D4" s="1">
-        <v>0.63380000000000003</v>
+        <v>0.40949999999999998</v>
       </c>
       <c r="E4" s="1">
-        <v>3.49E-2</v>
+        <v>5.3100000000000001E-2</v>
       </c>
       <c r="F4" s="1">
-        <v>7.5899999999999995E-2</v>
+        <v>0.2306</v>
       </c>
       <c r="G4" s="1">
-        <v>0.1031</v>
+        <v>0.15290000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>0.1074</v>
+        <v>0.13450000000000001</v>
       </c>
       <c r="I4" s="1">
-        <v>0.13919999999999999</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="J4" s="1">
-        <v>0.109</v>
+        <v>0.1168</v>
       </c>
       <c r="K4" s="1">
-        <v>0.1166</v>
+        <v>0.1036</v>
       </c>
       <c r="L4" s="1">
-        <v>0.1275</v>
+        <v>0.11550000000000001</v>
       </c>
       <c r="M4" s="1">
-        <v>0.1452</v>
+        <v>0.1173</v>
       </c>
       <c r="N4" s="1">
-        <v>0.1434</v>
+        <v>0.1216</v>
       </c>
       <c r="O4" s="1">
-        <v>0.15640000000000001</v>
+        <v>0.13320000000000001</v>
       </c>
       <c r="P4" s="1">
-        <v>0.11509999999999999</v>
+        <v>0.151</v>
       </c>
       <c r="Q4" s="1">
-        <v>0.30170000000000002</v>
+        <v>0.1651</v>
       </c>
       <c r="R4" s="1">
-        <v>0.29060000000000002</v>
+        <v>0.17230000000000001</v>
       </c>
       <c r="S4" s="1">
-        <v>0.26829999999999998</v>
+        <v>0.1956</v>
       </c>
       <c r="T4" s="1">
-        <v>0.34160000000000001</v>
+        <v>0.19850000000000001</v>
       </c>
       <c r="U4" s="1">
-        <v>0.77859999999999996</v>
+        <v>0.21290000000000001</v>
       </c>
       <c r="V4" s="1">
-        <v>0.93889999999999996</v>
+        <v>0.23269999999999999</v>
       </c>
       <c r="W4" s="1">
-        <v>0.99380000000000002</v>
+        <v>0.2271</v>
       </c>
       <c r="X4" s="1">
-        <v>1.1475</v>
-      </c>
-      <c r="Y4" s="1">
-        <v>1.1680999999999999</v>
-      </c>
-      <c r="Z4" s="1">
-        <v>1.054</v>
-      </c>
-      <c r="AA4" s="1">
-        <v>1.0703</v>
+        <v>0.22739999999999999</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="AB4" s="1" t="s">
         <v>10</v>
@@ -36468,127 +36470,127 @@
         <v>0.9</v>
       </c>
       <c r="C5" s="1">
-        <v>1.0176000000000001</v>
+        <v>2.1288999999999998</v>
       </c>
       <c r="D5" s="1">
-        <v>1.2543</v>
+        <v>0.84370000000000001</v>
       </c>
       <c r="E5" s="1">
-        <v>0</v>
+        <v>0.10150000000000001</v>
       </c>
       <c r="F5" s="1">
-        <v>8.2299999999999998E-2</v>
+        <v>8.8099999999999998E-2</v>
       </c>
       <c r="G5" s="1">
-        <v>0.40050000000000002</v>
+        <v>9.2399999999999996E-2</v>
       </c>
       <c r="H5" s="1">
-        <v>5.6899999999999999E-2</v>
+        <v>5.8900000000000001E-2</v>
       </c>
       <c r="I5" s="1">
-        <v>0.15679999999999999</v>
+        <v>6.2600000000000003E-2</v>
       </c>
       <c r="J5" s="1">
-        <v>5.3900000000000003E-2</v>
+        <v>7.1300000000000002E-2</v>
       </c>
       <c r="K5" s="1">
-        <v>4.8599999999999997E-2</v>
+        <v>7.4899999999999994E-2</v>
       </c>
       <c r="L5" s="1">
-        <v>5.7700000000000001E-2</v>
+        <v>7.9200000000000007E-2</v>
       </c>
       <c r="M5" s="1">
-        <v>5.4399999999999997E-2</v>
+        <v>8.7099999999999997E-2</v>
       </c>
       <c r="N5" s="1">
-        <v>7.9399999999999998E-2</v>
+        <v>9.6199999999999994E-2</v>
       </c>
       <c r="O5" s="1">
-        <v>9.6299999999999997E-2</v>
+        <v>0.1071</v>
       </c>
       <c r="P5" s="1">
-        <v>0.434</v>
+        <v>0.1038</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.28149999999999997</v>
+        <v>0.11070000000000001</v>
       </c>
       <c r="R5" s="1">
-        <v>0.42030000000000001</v>
+        <v>0.1187</v>
       </c>
       <c r="S5" s="1">
-        <v>1.1366000000000001</v>
+        <v>0.24779999999999999</v>
       </c>
       <c r="T5" s="1">
-        <v>1.0929</v>
+        <v>0.22650000000000001</v>
       </c>
       <c r="U5" s="1">
-        <v>0.99980000000000002</v>
+        <v>0.2114</v>
       </c>
       <c r="V5" s="1">
-        <v>1.0789</v>
+        <v>0.2472</v>
       </c>
       <c r="W5" s="1">
-        <v>1.1588000000000001</v>
+        <v>0.23150000000000001</v>
       </c>
       <c r="X5" s="1">
-        <v>1.0157</v>
+        <v>0.2218</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.68120000000000003</v>
+        <v>0.246</v>
       </c>
       <c r="Z5" s="1">
-        <v>1.0490999999999999</v>
+        <v>0.24260000000000001</v>
       </c>
       <c r="AA5" s="1">
-        <v>9.4643999999999995</v>
+        <v>0.27339999999999998</v>
       </c>
       <c r="AB5" s="1">
-        <v>21.874600000000001</v>
+        <v>0.18110000000000001</v>
       </c>
       <c r="AC5" s="1">
-        <v>1E-4</v>
+        <v>0.2858</v>
       </c>
       <c r="AD5" s="1">
-        <v>0.55389999999999995</v>
+        <v>0.29220000000000002</v>
       </c>
       <c r="AE5" s="1">
-        <v>0.48349999999999999</v>
+        <v>0.42480000000000001</v>
       </c>
       <c r="AF5" s="1">
-        <v>0.187</v>
+        <v>0.31819999999999998</v>
       </c>
       <c r="AG5" s="1">
-        <v>0.32</v>
+        <v>0.2175</v>
       </c>
       <c r="AH5" s="1">
-        <v>0.2671</v>
+        <v>0.25219999999999998</v>
       </c>
       <c r="AI5" s="1">
-        <v>0.18540000000000001</v>
+        <v>0.28060000000000002</v>
       </c>
       <c r="AJ5" s="1">
-        <v>0.62809999999999999</v>
+        <v>0.1883</v>
       </c>
       <c r="AK5" s="1">
-        <v>0.4582</v>
+        <v>0.1678</v>
       </c>
       <c r="AL5" s="1">
-        <v>0.20710000000000001</v>
+        <v>0.19059999999999999</v>
       </c>
       <c r="AM5" s="1">
-        <v>0.19189999999999999</v>
+        <v>0.17510000000000001</v>
       </c>
       <c r="AN5" s="1">
-        <v>0.69630000000000003</v>
-      </c>
-      <c r="AO5" s="1">
-        <v>0.69499999999999995</v>
-      </c>
-      <c r="AP5" s="1">
-        <v>0.62419999999999998</v>
-      </c>
-      <c r="AQ5" s="1">
-        <v>0.50829999999999997</v>
+        <v>0.2024</v>
+      </c>
+      <c r="AO5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ5" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="AR5" s="27" t="s">
         <v>10</v>
@@ -36620,151 +36622,151 @@
         <v>1</v>
       </c>
       <c r="C6" s="1">
-        <v>0.18190000000000001</v>
+        <v>3.2130999999999998</v>
       </c>
       <c r="D6" s="1">
-        <v>1.6163000000000001</v>
+        <v>1.8468</v>
       </c>
       <c r="E6" s="1">
-        <v>0.24160000000000001</v>
+        <v>7.6200000000000004E-2</v>
       </c>
       <c r="F6" s="1">
-        <v>1.0613999999999999</v>
+        <v>0.18540000000000001</v>
       </c>
       <c r="G6" s="1">
-        <v>8.4400000000000003E-2</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>1</v>
+        <v>0.36149999999999999</v>
+      </c>
+      <c r="H6" s="1">
+        <v>6.7900000000000002E-2</v>
       </c>
       <c r="I6" s="1">
-        <v>1.34E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="J6" s="1">
-        <v>5.7000000000000002E-3</v>
+        <v>2.1700000000000001E-2</v>
       </c>
       <c r="K6" s="1">
-        <v>2.6700000000000002E-2</v>
+        <v>1.9699999999999999E-2</v>
       </c>
       <c r="L6" s="1">
-        <v>2.87E-2</v>
+        <v>3.3099999999999997E-2</v>
       </c>
       <c r="M6" s="1">
-        <v>6.6100000000000006E-2</v>
+        <v>5.5399999999999998E-2</v>
       </c>
       <c r="N6" s="1">
-        <v>0.31109999999999999</v>
+        <v>7.7799999999999994E-2</v>
       </c>
       <c r="O6" s="1">
-        <v>0.36109999999999998</v>
+        <v>9.7799999999999998E-2</v>
       </c>
       <c r="P6" s="1">
+        <v>0.104</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0.1003</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0.1181</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0.2092</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0.2172</v>
+      </c>
+      <c r="U6" s="1">
+        <v>0.22589999999999999</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0.26129999999999998</v>
+      </c>
+      <c r="W6" s="27">
+        <v>0.2253</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0.25929999999999997</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>0.29010000000000002</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0.30299999999999999</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>0.253</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>0.30080000000000001</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>0.34439999999999998</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>0.35089999999999999</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>0.28960000000000002</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>0.25340000000000001</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>0.31690000000000002</v>
+      </c>
+      <c r="AI6" s="1">
+        <v>0.29520000000000002</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>0.34110000000000001</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>0.44769999999999999</v>
+      </c>
+      <c r="AL6" s="1">
+        <v>0.31009999999999999</v>
+      </c>
+      <c r="AM6" s="1">
+        <v>0.4728</v>
+      </c>
+      <c r="AN6" s="1">
         <v>0.43840000000000001</v>
       </c>
-      <c r="Q6" s="1">
-        <v>0.46610000000000001</v>
-      </c>
-      <c r="R6" s="1">
-        <v>0.75700000000000001</v>
-      </c>
-      <c r="S6" s="1">
-        <v>0.57040000000000002</v>
-      </c>
-      <c r="T6" s="1">
-        <v>0.75049999999999994</v>
-      </c>
-      <c r="U6" s="1">
-        <v>0.2833</v>
-      </c>
-      <c r="V6" s="1">
-        <v>0.22739999999999999</v>
-      </c>
-      <c r="W6" s="27">
-        <v>0.31330000000000002</v>
-      </c>
-      <c r="X6" s="1">
-        <v>0.60589999999999999</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>0.76290000000000002</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>7.4099999999999999E-2</v>
-      </c>
-      <c r="AA6" s="1">
-        <v>6.3799999999999996E-2</v>
-      </c>
-      <c r="AB6" s="1">
-        <v>4.48E-2</v>
-      </c>
-      <c r="AC6" s="1">
-        <v>0.21679999999999999</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>0.84489999999999998</v>
-      </c>
-      <c r="AE6" s="1">
-        <v>0.41749999999999998</v>
-      </c>
-      <c r="AF6" s="1">
-        <v>0.69240000000000002</v>
-      </c>
-      <c r="AG6" s="1">
-        <v>0.44319999999999998</v>
-      </c>
-      <c r="AH6" s="1">
-        <v>0.53180000000000005</v>
-      </c>
-      <c r="AI6" s="1">
-        <v>0.17019999999999999</v>
-      </c>
-      <c r="AJ6" s="1">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="AK6" s="1">
-        <v>0.15509999999999999</v>
-      </c>
-      <c r="AL6" s="1">
-        <v>0.1845</v>
-      </c>
-      <c r="AM6" s="1">
-        <v>0.17710000000000001</v>
-      </c>
-      <c r="AN6" s="1">
-        <v>0.62790000000000001</v>
-      </c>
       <c r="AO6" s="1">
-        <v>0.46539999999999998</v>
+        <v>0.33339999999999997</v>
       </c>
       <c r="AP6" s="1">
-        <v>0.74760000000000004</v>
+        <v>0.40949999999999998</v>
       </c>
       <c r="AQ6" s="1">
-        <v>0.63880000000000003</v>
+        <v>0.60640000000000005</v>
       </c>
       <c r="AR6" s="1">
-        <v>0.31290000000000001</v>
+        <v>0.64949999999999997</v>
       </c>
       <c r="AS6" s="1">
-        <v>0.60540000000000005</v>
+        <v>0.60729999999999995</v>
       </c>
       <c r="AT6" s="1">
-        <v>0.61880000000000002</v>
+        <v>0.5544</v>
       </c>
       <c r="AU6" s="27">
-        <v>0.54149999999999998</v>
+        <v>0.64629999999999999</v>
       </c>
       <c r="AV6" s="1">
-        <v>0.34620000000000001</v>
+        <v>0.58189999999999997</v>
       </c>
       <c r="AW6" s="1">
-        <v>0.33760000000000001</v>
+        <v>0.42670000000000002</v>
       </c>
       <c r="AX6" s="1">
-        <v>0.29409999999999997</v>
+        <v>0.31890000000000002</v>
       </c>
       <c r="AY6" s="1">
-        <v>0.42649999999999999</v>
+        <v>0.42699999999999999</v>
       </c>
     </row>
     <row r="7" spans="2:51" x14ac:dyDescent="0.3">
@@ -36772,151 +36774,151 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="C7" s="1">
-        <v>3.8108</v>
+        <v>3.9234</v>
       </c>
       <c r="D7" s="1">
-        <v>2.6926999999999999</v>
+        <v>3.3650000000000002</v>
       </c>
       <c r="E7" s="1">
-        <v>0.44059999999999999</v>
+        <v>0.29220000000000002</v>
       </c>
       <c r="F7" s="1">
-        <v>1.456</v>
+        <v>0.32140000000000002</v>
       </c>
       <c r="G7" s="1">
-        <v>8.1100000000000005E-2</v>
+        <v>0.92200000000000004</v>
       </c>
       <c r="H7" s="1">
-        <v>0.373</v>
+        <v>0.63580000000000003</v>
       </c>
       <c r="I7" s="1">
-        <v>0.30270000000000002</v>
+        <v>7.5899999999999995E-2</v>
       </c>
       <c r="J7" s="1">
-        <v>0.21629999999999999</v>
+        <v>0.247</v>
       </c>
       <c r="K7" s="1">
-        <v>0.1406</v>
+        <v>0.18459999999999999</v>
       </c>
       <c r="L7" s="1">
-        <v>1.1946000000000001</v>
+        <v>6.6799999999999998E-2</v>
       </c>
       <c r="M7" s="27">
-        <v>0</v>
-      </c>
-      <c r="N7" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>1</v>
+        <v>6.2399999999999997E-2</v>
+      </c>
+      <c r="N7" s="27">
+        <v>7.2800000000000004E-2</v>
+      </c>
+      <c r="O7" s="1">
+        <v>7.3300000000000004E-2</v>
       </c>
       <c r="P7" s="1">
-        <v>0.99780000000000002</v>
-      </c>
-      <c r="Q7" s="27" t="s">
-        <v>1</v>
+        <v>7.9100000000000004E-2</v>
+      </c>
+      <c r="Q7" s="27">
+        <v>8.3500000000000005E-2</v>
       </c>
       <c r="R7" s="1">
-        <v>0.95209999999999995</v>
+        <v>8.8099999999999998E-2</v>
       </c>
       <c r="S7" s="1">
-        <v>2.8405999999999998</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>1</v>
+        <v>9.1200000000000003E-2</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0.1067</v>
       </c>
       <c r="U7" s="1">
-        <v>0</v>
+        <v>0.1288</v>
       </c>
       <c r="V7" s="1">
-        <v>0.1517</v>
+        <v>0.1469</v>
       </c>
       <c r="W7" s="1">
-        <v>0.28050000000000003</v>
+        <v>0.18229999999999999</v>
       </c>
       <c r="X7" s="1">
-        <v>9.1999999999999998E-3</v>
+        <v>0.20930000000000001</v>
       </c>
       <c r="Y7" s="1">
-        <v>0.54320000000000002</v>
+        <v>0.1812</v>
       </c>
       <c r="Z7" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>1</v>
+        <v>0.16739999999999999</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>0.1605</v>
       </c>
       <c r="AB7" s="1">
-        <v>0.1305</v>
+        <v>0.157</v>
       </c>
       <c r="AC7" s="27">
-        <v>0.19570000000000001</v>
+        <v>0.15359999999999999</v>
       </c>
       <c r="AD7" s="1">
-        <v>0.1946</v>
+        <v>0.14549999999999999</v>
       </c>
       <c r="AE7" s="1">
-        <v>0.17810000000000001</v>
+        <v>0.157</v>
       </c>
       <c r="AF7" s="1">
-        <v>0.1651</v>
+        <v>0.16619999999999999</v>
       </c>
       <c r="AG7" s="1">
-        <v>0.1472</v>
+        <v>0.159</v>
       </c>
       <c r="AH7" s="1">
-        <v>0.17810000000000001</v>
+        <v>0.15620000000000001</v>
       </c>
       <c r="AI7" s="1">
-        <v>0.1822</v>
+        <v>0.16189999999999999</v>
       </c>
       <c r="AJ7" s="1">
-        <v>0.2127</v>
+        <v>0.16950000000000001</v>
       </c>
       <c r="AK7" s="1">
-        <v>0.20180000000000001</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="AL7" s="1">
-        <v>0.22459999999999999</v>
+        <v>0.2094</v>
       </c>
       <c r="AM7" s="1">
-        <v>0.27760000000000001</v>
+        <v>0.23680000000000001</v>
       </c>
       <c r="AN7" s="1">
-        <v>0.45469999999999999</v>
+        <v>0.25340000000000001</v>
       </c>
       <c r="AO7" s="1">
-        <v>0.4602</v>
+        <v>0.2923</v>
       </c>
       <c r="AP7" s="1">
-        <v>0.30159999999999998</v>
+        <v>0.30980000000000002</v>
       </c>
       <c r="AQ7" s="1">
-        <v>0.25009999999999999</v>
+        <v>0.34549999999999997</v>
       </c>
       <c r="AR7" s="1">
-        <v>0.4289</v>
+        <v>0.35299999999999998</v>
       </c>
       <c r="AS7" s="1">
-        <v>0.23749999999999999</v>
+        <v>0.3977</v>
       </c>
       <c r="AT7" s="1">
-        <v>0.34420000000000001</v>
+        <v>0.37530000000000002</v>
       </c>
       <c r="AU7" s="1">
-        <v>0.38600000000000001</v>
+        <v>0.3009</v>
       </c>
       <c r="AV7" s="1">
-        <v>0.28520000000000001</v>
+        <v>0.26690000000000003</v>
       </c>
       <c r="AW7" s="1">
-        <v>0.37490000000000001</v>
+        <v>0.26529999999999998</v>
       </c>
       <c r="AX7" s="1">
-        <v>0.22639999999999999</v>
+        <v>0.2387</v>
       </c>
       <c r="AY7" s="1">
-        <v>0.30480000000000002</v>
+        <v>0.24859999999999999</v>
       </c>
     </row>
     <row r="8" spans="2:51" x14ac:dyDescent="0.3">
@@ -36924,151 +36926,151 @@
         <v>1.2</v>
       </c>
       <c r="C8" s="1">
-        <v>3.9497</v>
+        <v>4.2980999999999998</v>
       </c>
       <c r="D8" s="1">
-        <v>4.0537999999999998</v>
+        <v>3.3997000000000002</v>
       </c>
       <c r="E8" s="1">
-        <v>3.4306000000000001</v>
+        <v>3.3980999999999999</v>
       </c>
       <c r="F8" s="1">
-        <v>2.4961000000000002</v>
+        <v>0.75890000000000002</v>
       </c>
       <c r="G8" s="1">
-        <v>0.30640000000000001</v>
+        <v>1.6400999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>1.4925999999999999</v>
+        <v>1.3318000000000001</v>
       </c>
       <c r="I8" s="1">
-        <v>1.4993000000000001</v>
+        <v>0.91039999999999999</v>
       </c>
       <c r="J8" s="1">
-        <v>0.49969999999999998</v>
+        <v>0.54620000000000002</v>
       </c>
       <c r="K8" s="1">
-        <v>0.20269999999999999</v>
+        <v>0.3755</v>
       </c>
       <c r="L8" s="1">
-        <v>0.28179999999999999</v>
+        <v>0.24729999999999999</v>
       </c>
       <c r="M8" s="1">
-        <v>0.18390000000000001</v>
+        <v>0.2041</v>
       </c>
       <c r="N8" s="27">
-        <v>1E-4</v>
+        <v>0.19620000000000001</v>
       </c>
       <c r="O8" s="1">
-        <v>0.378</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>1</v>
+        <v>0.31909999999999999</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0.1668</v>
       </c>
       <c r="Q8" s="1">
-        <v>0.55200000000000005</v>
+        <v>0.3538</v>
       </c>
       <c r="R8" s="1">
-        <v>0.24030000000000001</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>1</v>
+        <v>0.44159999999999999</v>
+      </c>
+      <c r="S8" s="1">
+        <v>0.23400000000000001</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0.3054</v>
       </c>
       <c r="U8" s="1">
-        <v>0.19189999999999999</v>
+        <v>3.7785000000000002</v>
       </c>
       <c r="V8" s="1">
+        <v>0.1777</v>
+      </c>
+      <c r="W8" s="1">
+        <v>0.2079</v>
+      </c>
+      <c r="X8" s="1">
+        <v>0.20860000000000001</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>0.20349999999999999</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>0.29089999999999999</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>0.25829999999999997</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>0.35439999999999999</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>0.25819999999999999</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>0.35349999999999998</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>0.37040000000000001</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ8" s="1">
         <v>0</v>
       </c>
-      <c r="W8" s="1">
+      <c r="AK8" s="1">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="AL8" s="1">
         <v>0</v>
       </c>
-      <c r="X8" s="1">
-        <v>3.7761999999999998</v>
-      </c>
-      <c r="Y8" s="1">
-        <v>0.22220000000000001</v>
-      </c>
-      <c r="Z8" s="1">
-        <v>0.68689999999999996</v>
-      </c>
-      <c r="AA8" s="1">
-        <v>0.29630000000000001</v>
-      </c>
-      <c r="AB8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="1">
-        <v>2.6435</v>
-      </c>
-      <c r="AD8" s="1">
-        <v>37.174599999999998</v>
-      </c>
-      <c r="AE8" s="1">
+      <c r="AM8" s="1">
         <v>0</v>
       </c>
-      <c r="AF8" s="1">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="AG8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="1">
-        <v>5.3315999999999999</v>
-      </c>
-      <c r="AI8" s="1">
-        <v>0.48449999999999999</v>
-      </c>
-      <c r="AJ8" s="1">
-        <v>1.6091</v>
-      </c>
-      <c r="AK8" s="1">
-        <v>5.5441000000000003</v>
-      </c>
-      <c r="AL8" s="1">
-        <v>0.58819999999999995</v>
-      </c>
-      <c r="AM8" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="AN8" s="1">
-        <v>0</v>
+        <v>8.2270000000000003</v>
       </c>
       <c r="AO8" s="1">
-        <v>0.51380000000000003</v>
+        <v>0.495</v>
       </c>
       <c r="AP8" s="1">
-        <v>0.61919999999999997</v>
+        <v>0.51019999999999999</v>
       </c>
       <c r="AQ8" s="1">
-        <v>0</v>
+        <v>0.38469999999999999</v>
       </c>
       <c r="AR8" s="1">
-        <v>0.43909999999999999</v>
+        <v>0.50170000000000003</v>
       </c>
       <c r="AS8" s="1">
-        <v>1.454</v>
+        <v>0.40310000000000001</v>
       </c>
       <c r="AT8" s="1">
-        <v>0.6492</v>
+        <v>0.4345</v>
       </c>
       <c r="AU8" s="1">
-        <v>0.79120000000000001</v>
+        <v>0.5504</v>
       </c>
       <c r="AV8" s="1">
-        <v>0.59860000000000002</v>
+        <v>0.75</v>
       </c>
       <c r="AW8" s="1">
-        <v>0.79579999999999995</v>
+        <v>0.63200000000000001</v>
       </c>
       <c r="AX8" s="1">
-        <v>0.43259999999999998</v>
+        <v>0.7258</v>
       </c>
       <c r="AY8" s="1">
-        <v>0.81810000000000005</v>
+        <v>0.61970000000000003</v>
       </c>
     </row>
     <row r="9" spans="2:51" x14ac:dyDescent="0.3">
@@ -37079,145 +37081,145 @@
         <v>10</v>
       </c>
       <c r="D9" s="1">
-        <v>3.6438999999999999</v>
+        <v>3.94</v>
       </c>
       <c r="E9" s="1">
-        <v>3.6453000000000002</v>
+        <v>3.5607000000000002</v>
       </c>
       <c r="F9" s="1">
-        <v>4.1271000000000004</v>
+        <v>3.0017</v>
       </c>
       <c r="G9" s="1">
-        <v>0.79430000000000001</v>
+        <v>2.5937000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>2.5872999999999999</v>
+        <v>2.2088999999999999</v>
       </c>
       <c r="I9" s="1">
-        <v>0.42980000000000002</v>
+        <v>1.8654999999999999</v>
       </c>
       <c r="J9" s="1">
-        <v>1.0133000000000001</v>
+        <v>1.4859</v>
       </c>
       <c r="K9" s="1">
-        <v>0.44409999999999999</v>
+        <v>0.61170000000000002</v>
       </c>
       <c r="L9" s="1">
-        <v>1.4812000000000001</v>
+        <v>0.56820000000000004</v>
       </c>
       <c r="M9" s="1">
-        <v>0.4163</v>
+        <v>0.49409999999999998</v>
       </c>
       <c r="N9" s="1">
-        <v>0.44230000000000003</v>
+        <v>0.55830000000000002</v>
       </c>
       <c r="O9" s="1">
-        <v>0.42730000000000001</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="P9" s="1">
-        <v>5.4199999999999998E-2</v>
+        <v>0.48420000000000002</v>
       </c>
       <c r="Q9" s="1">
-        <v>0.6915</v>
+        <v>1.0736000000000001</v>
       </c>
       <c r="R9" s="1">
-        <v>0.24540000000000001</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>1</v>
+        <v>0.38379999999999997</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0.38379999999999997</v>
       </c>
       <c r="T9" s="1">
-        <v>0.32700000000000001</v>
+        <v>0.34689999999999999</v>
       </c>
       <c r="U9" s="1">
-        <v>0.43519999999999998</v>
+        <v>0.40050000000000002</v>
       </c>
       <c r="V9" s="1">
-        <v>0.25380000000000003</v>
+        <v>0.30649999999999999</v>
       </c>
       <c r="W9" s="1">
-        <v>0.38250000000000001</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>1</v>
+        <v>0.42359999999999998</v>
+      </c>
+      <c r="X9" s="1">
+        <v>0.50190000000000001</v>
       </c>
       <c r="Y9" s="1">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Z9" s="1" t="s">
-        <v>1</v>
+        <v>1.9146000000000001</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>0.64270000000000005</v>
       </c>
       <c r="AA9" s="1">
-        <v>0.67420000000000002</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="1">
-        <v>0.53710000000000002</v>
+        <v>0.62990000000000002</v>
       </c>
       <c r="AC9" s="1">
         <v>0</v>
       </c>
       <c r="AD9" s="1">
-        <v>6.3399999999999998E-2</v>
+        <v>0.37030000000000002</v>
       </c>
       <c r="AE9" s="1">
-        <v>0.51280000000000003</v>
+        <v>0.3266</v>
       </c>
       <c r="AF9" s="1">
-        <v>0.65400000000000003</v>
+        <v>0.621</v>
       </c>
       <c r="AG9" s="27">
-        <v>0.57720000000000005</v>
+        <v>0</v>
       </c>
       <c r="AH9" s="1">
-        <v>0.57840000000000003</v>
-      </c>
-      <c r="AI9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ9" s="1" t="s">
-        <v>1</v>
+        <v>0.51470000000000005</v>
+      </c>
+      <c r="AI9" s="1">
+        <v>0.51390000000000002</v>
+      </c>
+      <c r="AJ9" s="1">
+        <v>0.80030000000000001</v>
       </c>
       <c r="AK9" s="1">
-        <v>6.7699999999999996E-2</v>
+        <v>0.85770000000000002</v>
       </c>
       <c r="AL9" s="27">
+        <v>0.95130000000000003</v>
+      </c>
+      <c r="AM9" s="1">
         <v>0</v>
       </c>
-      <c r="AM9" s="1">
-        <v>8.0000000000000004E-4</v>
-      </c>
       <c r="AN9" s="1">
-        <v>0.83299999999999996</v>
+        <v>7.1083999999999996</v>
       </c>
       <c r="AO9" s="27">
-        <v>0.93920000000000003</v>
+        <v>0.44209999999999999</v>
       </c>
       <c r="AP9" s="1">
-        <v>0.47610000000000002</v>
+        <v>0</v>
       </c>
       <c r="AQ9" s="1">
-        <v>1.0206999999999999</v>
-      </c>
-      <c r="AR9" s="1">
-        <v>0.72850000000000004</v>
-      </c>
-      <c r="AS9" s="1">
-        <v>1.1082000000000001</v>
+        <v>0.52470000000000006</v>
+      </c>
+      <c r="AR9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS9" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="AT9" s="1">
-        <v>1.0686</v>
+        <v>1E-4</v>
       </c>
       <c r="AU9" s="1">
-        <v>1.083</v>
+        <v>3.6071</v>
       </c>
       <c r="AV9" s="1">
-        <v>1.2529999999999999</v>
+        <v>0.5141</v>
       </c>
       <c r="AW9" s="1">
-        <v>1.4253</v>
+        <v>0.50560000000000005</v>
       </c>
       <c r="AX9" s="27">
-        <v>1.0018</v>
+        <v>0.63619999999999999</v>
       </c>
       <c r="AY9" s="1">
         <v>0</v>
@@ -37234,145 +37236,145 @@
         <v>10</v>
       </c>
       <c r="E10" s="1">
-        <v>2.0821999999999998</v>
+        <v>4.0444000000000004</v>
       </c>
       <c r="F10" s="1">
-        <v>3.6541999999999999</v>
+        <v>3.4895999999999998</v>
       </c>
       <c r="G10" s="1">
-        <v>1.5570999999999999</v>
+        <v>3.2042999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>3.0002</v>
+        <v>2.6141999999999999</v>
       </c>
       <c r="I10" s="1">
-        <v>2.3376000000000001</v>
+        <v>2.7113</v>
       </c>
       <c r="J10" s="1">
-        <v>1.8293999999999999</v>
+        <v>2.4849999999999999</v>
       </c>
       <c r="K10" s="1">
-        <v>1.0874999999999999</v>
+        <v>2.2877999999999998</v>
       </c>
       <c r="L10" s="1">
-        <v>2.5209999999999999</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="M10" s="1">
-        <v>1.425</v>
+        <v>0.79930000000000001</v>
       </c>
       <c r="N10" s="1">
-        <v>0.82830000000000004</v>
+        <v>0.96840000000000004</v>
       </c>
       <c r="O10" s="1">
-        <v>1.6578999999999999</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="P10" s="1">
-        <v>0.75160000000000005</v>
+        <v>0.62949999999999995</v>
       </c>
       <c r="Q10" s="1">
-        <v>0.87170000000000003</v>
+        <v>0.54449999999999998</v>
       </c>
       <c r="R10" s="1">
-        <v>0.64129999999999998</v>
+        <v>0.77559999999999996</v>
       </c>
       <c r="S10" s="1">
-        <v>0.65880000000000005</v>
+        <v>1.4803999999999999</v>
       </c>
       <c r="T10" s="27">
-        <v>0.40739999999999998</v>
+        <v>0.36709999999999998</v>
       </c>
       <c r="U10" s="1">
-        <v>1.1298999999999999</v>
+        <v>0.95409999999999995</v>
       </c>
       <c r="V10" s="1">
         <v>0</v>
       </c>
       <c r="W10" s="1">
-        <v>0.7339</v>
+        <v>0.73160000000000003</v>
       </c>
       <c r="X10" s="1">
-        <v>0.80289999999999995</v>
+        <v>0.4128</v>
       </c>
       <c r="Y10" s="1">
-        <v>0.40849999999999997</v>
+        <v>0.4914</v>
       </c>
       <c r="Z10" s="1">
-        <v>0.44490000000000002</v>
+        <v>1.1404000000000001</v>
       </c>
       <c r="AA10" s="1">
-        <v>0.73909999999999998</v>
-      </c>
-      <c r="AB10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="1" t="s">
-        <v>1</v>
+        <v>0.38</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>0.54020000000000001</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>1.3649</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>0.84719999999999995</v>
       </c>
       <c r="AE10" s="1">
-        <v>2.6507000000000001</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="AF10" s="1">
-        <v>3.7600000000000001E-2</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="AG10" s="1">
-        <v>3.0590999999999999</v>
+        <v>0.69210000000000005</v>
       </c>
       <c r="AH10" s="1">
-        <v>1.5609</v>
+        <v>0.70350000000000001</v>
       </c>
       <c r="AI10" s="1">
-        <v>0</v>
+        <v>3.2906</v>
       </c>
       <c r="AJ10" s="1">
-        <v>0.85940000000000005</v>
+        <v>0.50429999999999997</v>
       </c>
       <c r="AK10" s="1">
-        <v>1.2902</v>
+        <v>0.60929999999999995</v>
       </c>
       <c r="AL10" s="1">
-        <v>1.0537000000000001</v>
+        <v>0.6714</v>
       </c>
       <c r="AM10" s="1">
-        <v>1.6720999999999999</v>
+        <v>0.90310000000000001</v>
       </c>
       <c r="AN10" s="1">
-        <v>1.7461</v>
+        <v>0.65590000000000004</v>
       </c>
       <c r="AO10" s="1">
-        <v>1.8858999999999999</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="AP10" s="1">
-        <v>2.8163</v>
-      </c>
-      <c r="AQ10" s="1" t="s">
-        <v>1</v>
+        <v>2.8201999999999998</v>
+      </c>
+      <c r="AQ10" s="1">
+        <v>0.49380000000000002</v>
       </c>
       <c r="AR10" s="1">
-        <v>0</v>
+        <v>1.3052999999999999</v>
       </c>
       <c r="AS10" s="1">
-        <v>2.375</v>
+        <v>1.8972</v>
       </c>
       <c r="AT10" s="1">
-        <v>0</v>
+        <v>2.5676000000000001</v>
       </c>
       <c r="AU10" s="27">
         <v>0</v>
       </c>
       <c r="AV10" s="1">
-        <v>4.7919999999999998</v>
+        <v>1.4121999999999999</v>
       </c>
       <c r="AW10" s="1">
-        <v>0.69130000000000003</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="AX10" s="1">
-        <v>1.7847999999999999</v>
+        <v>0.50570000000000004</v>
       </c>
       <c r="AY10" s="1">
-        <v>1.0371999999999999</v>
+        <v>1.2683</v>
       </c>
     </row>
     <row r="11" spans="2:51" x14ac:dyDescent="0.3">
@@ -37389,142 +37391,142 @@
         <v>10</v>
       </c>
       <c r="F11" s="27">
-        <v>6.0301999999999998</v>
+        <v>4.3429000000000002</v>
       </c>
       <c r="G11" s="1">
-        <v>4.2361000000000004</v>
+        <v>3.6151</v>
       </c>
       <c r="H11" s="1">
-        <v>2.9224999999999999</v>
+        <v>2.8711000000000002</v>
       </c>
       <c r="I11" s="1">
-        <v>2.0474000000000001</v>
+        <v>2.4117999999999999</v>
       </c>
       <c r="J11" s="1">
-        <v>2.1238000000000001</v>
+        <v>2.1404000000000001</v>
       </c>
       <c r="K11" s="1">
-        <v>2.0649000000000002</v>
+        <v>2.6095999999999999</v>
       </c>
       <c r="L11" s="1">
-        <v>5.0827</v>
+        <v>1.6680999999999999</v>
       </c>
       <c r="M11" s="1">
-        <v>1.3683000000000001</v>
+        <v>3.0341</v>
       </c>
       <c r="N11" s="1">
-        <v>1.4823999999999999</v>
+        <v>1.1910000000000001</v>
       </c>
       <c r="O11" s="1">
-        <v>0.58199999999999996</v>
+        <v>1.982</v>
       </c>
       <c r="P11" s="1">
-        <v>3.3035000000000001</v>
+        <v>1.1950000000000001</v>
       </c>
       <c r="Q11" s="1">
-        <v>0.86880000000000002</v>
+        <v>0.90459999999999996</v>
       </c>
       <c r="R11" s="1">
-        <v>0.67390000000000005</v>
+        <v>0.86260000000000003</v>
       </c>
       <c r="S11" s="1">
-        <v>0.94740000000000002</v>
+        <v>1.9248000000000001</v>
       </c>
       <c r="T11" s="1">
-        <v>1.5065999999999999</v>
+        <v>0.64939999999999998</v>
       </c>
       <c r="U11" s="1">
-        <v>0.72250000000000003</v>
+        <v>0.66</v>
       </c>
       <c r="V11" s="27">
-        <v>0.7359</v>
+        <v>0.64900000000000002</v>
       </c>
       <c r="W11" s="1">
-        <v>2.0626000000000002</v>
+        <v>1.3017000000000001</v>
       </c>
       <c r="X11" s="1">
-        <v>0.16089999999999999</v>
+        <v>1.7128000000000001</v>
       </c>
       <c r="Y11" s="1">
-        <v>0.56869999999999998</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="1">
-        <v>0.46360000000000001</v>
+        <v>1.0865</v>
       </c>
       <c r="AA11" s="1">
-        <v>1.8786</v>
+        <v>0.45150000000000001</v>
       </c>
       <c r="AB11" s="1">
-        <v>1.2332000000000001</v>
+        <v>0.45929999999999999</v>
       </c>
       <c r="AC11" s="1">
-        <v>1.1167</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="1">
-        <v>0.58579999999999999</v>
+        <v>2.3050999999999999</v>
       </c>
       <c r="AE11" s="1">
-        <v>0.88239999999999996</v>
+        <v>0.45329999999999998</v>
       </c>
       <c r="AF11" s="1">
-        <v>0.65910000000000002</v>
-      </c>
-      <c r="AG11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH11" s="1" t="s">
-        <v>1</v>
+        <v>0.86519999999999997</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>2.5017999999999998</v>
+      </c>
+      <c r="AH11" s="1">
+        <v>0.93030000000000002</v>
       </c>
       <c r="AI11" s="1">
-        <v>0</v>
+        <v>0.7379</v>
       </c>
       <c r="AJ11" s="1">
-        <v>0</v>
+        <v>2.3908</v>
       </c>
       <c r="AK11" s="1">
-        <v>0.24399999999999999</v>
+        <v>0.4617</v>
       </c>
       <c r="AL11" s="1">
-        <v>1.1727000000000001</v>
+        <v>1.3895</v>
       </c>
       <c r="AM11" s="27">
-        <v>1.7061999999999999</v>
+        <v>0.6643</v>
       </c>
       <c r="AN11" s="1">
-        <v>3.3875000000000002</v>
+        <v>1.1874</v>
       </c>
       <c r="AO11" s="1">
-        <v>1.0588</v>
+        <v>1.5118</v>
       </c>
       <c r="AP11" s="1">
-        <v>1.4830000000000001</v>
+        <v>0.91269999999999996</v>
       </c>
       <c r="AQ11" s="1">
-        <v>1.3163</v>
+        <v>1.0349999999999999</v>
       </c>
       <c r="AR11" s="1">
-        <v>2.3450000000000002</v>
+        <v>0.49940000000000001</v>
       </c>
       <c r="AS11" s="1">
-        <v>2.2336</v>
+        <v>1.0958000000000001</v>
       </c>
       <c r="AT11" s="27">
-        <v>2.5207000000000002</v>
+        <v>2.1823999999999999</v>
       </c>
       <c r="AU11" s="1">
-        <v>6.4222000000000001</v>
+        <v>0.5413</v>
       </c>
       <c r="AV11" s="1">
-        <v>6.7850000000000001</v>
+        <v>1.9802999999999999</v>
       </c>
       <c r="AW11" s="1">
-        <v>7.7743000000000002</v>
+        <v>1E-3</v>
       </c>
       <c r="AX11" s="1">
-        <v>7.2700000000000001E-2</v>
+        <v>0.62539999999999996</v>
       </c>
       <c r="AY11" s="27">
-        <v>1.2968</v>
+        <v>1.1460999999999999</v>
       </c>
     </row>
     <row r="12" spans="2:51" x14ac:dyDescent="0.3">
@@ -37544,139 +37546,139 @@
         <v>10</v>
       </c>
       <c r="G12" s="27">
-        <v>14.641999999999999</v>
+        <v>6.2588999999999997</v>
       </c>
       <c r="H12" s="27">
-        <v>3.1795</v>
+        <v>4.6124999999999998</v>
       </c>
       <c r="I12" s="1">
-        <v>2.0049000000000001</v>
+        <v>3.5533000000000001</v>
       </c>
       <c r="J12" s="1">
-        <v>2.0059999999999998</v>
+        <v>2.1019999999999999</v>
       </c>
       <c r="K12" s="1">
-        <v>3.6341000000000001</v>
+        <v>0.74239999999999995</v>
       </c>
       <c r="L12" s="1">
-        <v>1.3158000000000001</v>
+        <v>2.9658000000000002</v>
       </c>
       <c r="M12" s="1">
-        <v>2.0931000000000002</v>
+        <v>2.3853</v>
       </c>
       <c r="N12" s="1">
-        <v>4.8594999999999997</v>
+        <v>4.0275999999999996</v>
       </c>
       <c r="O12" s="1">
-        <v>2.0099</v>
+        <v>1.5636000000000001</v>
       </c>
       <c r="P12" s="1">
-        <v>1.3549</v>
+        <v>1.4409000000000001</v>
       </c>
       <c r="Q12" s="1">
-        <v>1.6738999999999999</v>
+        <v>2.8153000000000001</v>
       </c>
       <c r="R12" s="1">
-        <v>2.3797999999999999</v>
+        <v>1.8919999999999999</v>
       </c>
       <c r="S12" s="27">
-        <v>2.1640999999999999</v>
+        <v>0.72870000000000001</v>
       </c>
       <c r="T12" s="1">
-        <v>4.8112000000000004</v>
+        <v>2.0461999999999998</v>
       </c>
       <c r="U12" s="1">
-        <v>1.6035999999999999</v>
+        <v>2.3485</v>
       </c>
       <c r="V12" s="1">
-        <v>0.69350000000000001</v>
+        <v>0.83479999999999999</v>
       </c>
       <c r="W12" s="1">
-        <v>0.97160000000000002</v>
+        <v>1.9706999999999999</v>
       </c>
       <c r="X12" s="1">
-        <v>3.4666999999999999</v>
+        <v>0.93659999999999999</v>
       </c>
       <c r="Y12" s="1">
-        <v>7.1177000000000001</v>
-      </c>
-      <c r="Z12" s="1" t="s">
-        <v>1</v>
+        <v>1.6026</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>1.9168000000000001</v>
       </c>
       <c r="AA12" s="27">
-        <v>0</v>
+        <v>0.68459999999999999</v>
       </c>
       <c r="AB12" s="1">
         <v>0</v>
       </c>
       <c r="AC12" s="1">
-        <v>0.36520000000000002</v>
+        <v>1.1008</v>
       </c>
       <c r="AD12" s="1">
-        <v>0.99060000000000004</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="AE12" s="1">
-        <v>2.9399999999999999E-2</v>
+        <v>0.44990000000000002</v>
       </c>
       <c r="AF12" s="1">
-        <v>0.98260000000000003</v>
+        <v>0.44940000000000002</v>
       </c>
       <c r="AG12" s="1">
-        <v>1.8512999999999999</v>
+        <v>0.1386</v>
       </c>
       <c r="AH12" s="1">
-        <v>0.62409999999999999</v>
+        <v>1.3091999999999999</v>
       </c>
       <c r="AI12" s="1">
-        <v>1.6848000000000001</v>
+        <v>1.4804999999999999</v>
       </c>
       <c r="AJ12" s="1">
-        <v>2.6337999999999999</v>
+        <v>2.2677</v>
       </c>
       <c r="AK12" s="1">
-        <v>6.7417999999999996</v>
-      </c>
-      <c r="AL12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM12" s="1" t="s">
-        <v>1</v>
+        <v>6.9824999999999999</v>
+      </c>
+      <c r="AL12" s="1">
+        <v>7.2099999999999997E-2</v>
+      </c>
+      <c r="AM12" s="1">
+        <v>1.5896999999999999</v>
       </c>
       <c r="AN12" s="1">
-        <v>1.9638</v>
+        <v>0.58079999999999998</v>
       </c>
       <c r="AO12" s="1">
-        <v>0</v>
+        <v>1.7312000000000001</v>
       </c>
       <c r="AP12" s="1">
-        <v>1.4569000000000001</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="AQ12" s="1">
-        <v>1.0064</v>
+        <v>1.8069999999999999</v>
       </c>
       <c r="AR12" s="1">
-        <v>1.9952000000000001</v>
+        <v>0.62070000000000003</v>
       </c>
       <c r="AS12" s="27">
-        <v>4.5495000000000001</v>
+        <v>2.3826999999999998</v>
       </c>
       <c r="AT12" s="1">
-        <v>13.2186</v>
+        <v>2.6516999999999999</v>
       </c>
       <c r="AU12" s="1">
-        <v>0.68740000000000001</v>
+        <v>1.3553999999999999</v>
       </c>
       <c r="AV12" s="1">
-        <v>2.5583999999999998</v>
+        <v>0.77390000000000003</v>
       </c>
       <c r="AW12" s="27">
-        <v>0.58699999999999997</v>
+        <v>1.0397000000000001</v>
       </c>
       <c r="AX12" s="1">
-        <v>1.9438</v>
+        <v>1.7087000000000001</v>
       </c>
       <c r="AY12" s="1">
-        <v>0.66100000000000003</v>
+        <v>0.59109999999999996</v>
       </c>
     </row>
     <row r="13" spans="2:51" x14ac:dyDescent="0.3">
@@ -37702,133 +37704,133 @@
         <v>10</v>
       </c>
       <c r="I13" s="1">
-        <v>6.4832999999999998</v>
+        <v>14.536799999999999</v>
       </c>
       <c r="J13" s="1">
-        <v>7.3826000000000001</v>
+        <v>8.8678000000000008</v>
       </c>
       <c r="K13" s="1">
-        <v>18.001799999999999</v>
+        <v>8.0893999999999995</v>
       </c>
       <c r="L13" s="1">
-        <v>6.39</v>
+        <v>5.4691000000000001</v>
       </c>
       <c r="M13" s="1">
-        <v>8.0501000000000005</v>
+        <v>4.7931999999999997</v>
       </c>
       <c r="N13" s="1">
-        <v>12.8711</v>
+        <v>9.9184999999999999</v>
       </c>
       <c r="O13" s="1">
-        <v>4.2380000000000004</v>
+        <v>3.4487000000000001</v>
       </c>
       <c r="P13" s="1">
-        <v>5.3880999999999997</v>
+        <v>4.9039999999999999</v>
       </c>
       <c r="Q13" s="1">
-        <v>7.3973000000000004</v>
+        <v>3.7160000000000002</v>
       </c>
       <c r="R13" s="1">
-        <v>3.1080999999999999</v>
+        <v>3.4689999999999999</v>
       </c>
       <c r="S13" s="1">
-        <v>4.0316000000000001</v>
+        <v>2.9378000000000002</v>
       </c>
       <c r="T13" s="1">
-        <v>3.5933000000000002</v>
+        <v>1.0744</v>
       </c>
       <c r="U13" s="1">
-        <v>8.8750999999999998</v>
+        <v>4.4128999999999996</v>
       </c>
       <c r="V13" s="1">
-        <v>0.23150000000000001</v>
+        <v>4.2117000000000004</v>
       </c>
       <c r="W13" s="1">
-        <v>2.0225</v>
+        <v>1.6334</v>
       </c>
       <c r="X13" s="1">
-        <v>4.0815000000000001</v>
+        <v>2.0807000000000002</v>
       </c>
       <c r="Y13" s="1">
-        <v>1.6828000000000001</v>
+        <v>1.9194</v>
       </c>
       <c r="Z13" s="1">
-        <v>4.3449999999999998</v>
+        <v>2.2595999999999998</v>
       </c>
       <c r="AA13" s="1">
-        <v>17.245200000000001</v>
+        <v>4.3132999999999999</v>
       </c>
       <c r="AB13" s="1">
-        <v>3.7557</v>
-      </c>
-      <c r="AC13" s="1" t="s">
-        <v>1</v>
+        <v>4.3681000000000001</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>3.5623999999999998</v>
       </c>
       <c r="AD13" s="1">
+        <v>2.2450000000000001</v>
+      </c>
+      <c r="AE13" s="1">
         <v>0</v>
       </c>
-      <c r="AE13" s="1">
-        <v>2.2806000000000002</v>
-      </c>
       <c r="AF13" s="1">
-        <v>1.8948</v>
+        <v>2.2618</v>
       </c>
       <c r="AG13" s="1">
+        <v>0.61899999999999999</v>
+      </c>
+      <c r="AH13" s="1">
+        <v>2.2993999999999999</v>
+      </c>
+      <c r="AI13" s="27">
+        <v>1.1415999999999999</v>
+      </c>
+      <c r="AJ13" s="27">
+        <v>0.1762</v>
+      </c>
+      <c r="AK13" s="1">
+        <v>1.1806000000000001</v>
+      </c>
+      <c r="AL13" s="1">
+        <v>2.2824</v>
+      </c>
+      <c r="AM13" s="1">
+        <v>2.9093</v>
+      </c>
+      <c r="AN13" s="1">
+        <v>8.2979000000000003</v>
+      </c>
+      <c r="AO13" s="1">
+        <v>8.3020999999999994</v>
+      </c>
+      <c r="AP13" s="1">
         <v>0</v>
       </c>
-      <c r="AH13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="27">
-        <v>4.1863000000000001</v>
-      </c>
-      <c r="AJ13" s="27">
-        <v>1.9915</v>
-      </c>
-      <c r="AK13" s="1">
-        <v>5.4467999999999996</v>
-      </c>
-      <c r="AL13" s="1">
-        <v>1.0134000000000001</v>
-      </c>
-      <c r="AM13" s="1">
-        <v>4.1571999999999996</v>
-      </c>
-      <c r="AN13" s="1">
-        <v>11.259399999999999</v>
-      </c>
-      <c r="AO13" s="1">
-        <v>5.0186000000000002</v>
-      </c>
-      <c r="AP13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQ13" s="1" t="s">
-        <v>1</v>
+      <c r="AQ13" s="1">
+        <v>1.7836000000000001</v>
       </c>
       <c r="AR13" s="1">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AS13" s="1">
-        <v>1E-4</v>
+        <v>3.1976</v>
       </c>
       <c r="AT13" s="1">
-        <v>0</v>
+        <v>1.5986</v>
       </c>
       <c r="AU13" s="1">
-        <v>1.3156000000000001</v>
+        <v>0.84740000000000004</v>
       </c>
       <c r="AV13" s="27">
-        <v>0.78990000000000005</v>
+        <v>0.7661</v>
       </c>
       <c r="AW13" s="27">
-        <v>7.5115999999999996</v>
+        <v>0.77200000000000002</v>
       </c>
       <c r="AX13" s="1">
-        <v>11.757099999999999</v>
+        <v>3.2881999999999998</v>
       </c>
       <c r="AY13" s="1">
-        <v>20.764900000000001</v>
+        <v>7.3147000000000002</v>
       </c>
     </row>
     <row r="14" spans="2:51" x14ac:dyDescent="0.3">
@@ -37863,124 +37865,124 @@
         <v>10</v>
       </c>
       <c r="L14" s="1">
-        <v>23.657800000000002</v>
+        <v>14.117900000000001</v>
       </c>
       <c r="M14" s="1">
-        <v>20.401900000000001</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>1</v>
+        <v>13.0778</v>
+      </c>
+      <c r="N14" s="1">
+        <v>19.805099999999999</v>
       </c>
       <c r="O14" s="1">
-        <v>9.6194000000000006</v>
+        <v>8.0381999999999998</v>
       </c>
       <c r="P14" s="1">
-        <v>15.598800000000001</v>
+        <v>22.304200000000002</v>
       </c>
       <c r="Q14" s="1">
-        <v>16.6907</v>
+        <v>5.3121999999999998</v>
       </c>
       <c r="R14" s="1">
-        <v>4.5891999999999999</v>
+        <v>20.6311</v>
       </c>
       <c r="S14" s="1">
-        <v>2.0707</v>
+        <v>7.8932000000000002</v>
       </c>
       <c r="T14" s="1">
-        <v>31.975899999999999</v>
+        <v>6.4638999999999998</v>
       </c>
       <c r="U14" s="1">
-        <v>8.6188000000000002</v>
+        <v>4.3616000000000001</v>
       </c>
       <c r="V14" s="27">
-        <v>24.4299</v>
+        <v>17.029199999999999</v>
       </c>
       <c r="W14" s="1">
-        <v>1.7025999999999999</v>
+        <v>0.996</v>
       </c>
       <c r="X14" s="1">
-        <v>3.3144999999999998</v>
+        <v>3.7534000000000001</v>
       </c>
       <c r="Y14" s="1">
-        <v>10.4503</v>
+        <v>2.7313999999999998</v>
       </c>
       <c r="Z14" s="1">
-        <v>1.2309000000000001</v>
+        <v>2.9327000000000001</v>
       </c>
       <c r="AA14" s="1">
-        <v>17.7729</v>
+        <v>0.69040000000000001</v>
       </c>
       <c r="AB14" s="1">
-        <v>17.6557</v>
+        <v>4.7192999999999996</v>
       </c>
       <c r="AC14" s="1">
-        <v>8.3867999999999991</v>
+        <v>4.1318000000000001</v>
       </c>
       <c r="AD14" s="1">
-        <v>62.529000000000003</v>
-      </c>
-      <c r="AE14" s="1" t="s">
-        <v>1</v>
+        <v>20.351500000000001</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>14.003399999999999</v>
       </c>
       <c r="AF14" s="1">
+        <v>2.6709999999999998</v>
+      </c>
+      <c r="AG14" s="1">
         <v>0</v>
       </c>
-      <c r="AG14" s="1">
-        <v>2.5667</v>
-      </c>
       <c r="AH14" s="1">
-        <v>1.9107000000000001</v>
+        <v>0.45200000000000001</v>
       </c>
       <c r="AI14" s="1">
-        <v>5.7564000000000002</v>
+        <v>1.4443999999999999</v>
       </c>
       <c r="AJ14" s="1">
-        <v>8.0000000000000004E-4</v>
+        <v>0.50280000000000002</v>
       </c>
       <c r="AK14" s="1">
-        <v>1.6851</v>
+        <v>1.9049</v>
       </c>
       <c r="AL14" s="1">
-        <v>11.7988</v>
+        <v>8.9123999999999999</v>
       </c>
       <c r="AM14" s="27">
-        <v>1.9838</v>
+        <v>0.29720000000000002</v>
       </c>
       <c r="AN14" s="1">
-        <v>1.7907999999999999</v>
+        <v>1.2787999999999999</v>
       </c>
       <c r="AO14" s="27">
-        <v>0.44550000000000001</v>
+        <v>4.3825000000000003</v>
       </c>
       <c r="AP14" s="1">
-        <v>26.293199999999999</v>
+        <v>18.883400000000002</v>
       </c>
       <c r="AQ14" s="1">
-        <v>27.499400000000001</v>
+        <v>22.629300000000001</v>
       </c>
       <c r="AR14" s="1">
-        <v>8.3760999999999992</v>
+        <v>15.587199999999999</v>
       </c>
       <c r="AS14" s="1">
-        <v>22.137</v>
+        <v>11.084</v>
       </c>
       <c r="AT14" s="27">
-        <v>11.621600000000001</v>
-      </c>
-      <c r="AU14" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AU14" s="1">
+        <v>1.1409</v>
       </c>
       <c r="AV14" s="1">
-        <v>0</v>
+        <v>1.1277999999999999</v>
       </c>
       <c r="AW14" s="1">
-        <v>0.99619999999999997</v>
+        <v>2.2433999999999998</v>
       </c>
       <c r="AX14" s="1">
-        <v>1.036</v>
+        <v>11.0481</v>
       </c>
       <c r="AY14" s="1">
-        <v>0.26019999999999999</v>
+        <v>1.0991</v>
       </c>
     </row>
     <row r="15" spans="2:51" x14ac:dyDescent="0.3">
@@ -38033,124 +38035,124 @@
         <v>10</v>
       </c>
       <c r="R15" s="1">
-        <v>13.236000000000001</v>
+        <v>29.6143</v>
       </c>
       <c r="S15" s="1">
-        <v>13.3667</v>
+        <v>14.8568</v>
       </c>
       <c r="T15" s="1">
-        <v>46.550800000000002</v>
+        <v>9.9928000000000008</v>
       </c>
       <c r="U15" s="1">
-        <v>3.4742000000000002</v>
+        <v>11.640599999999999</v>
       </c>
       <c r="V15" s="1">
-        <v>66.898399999999995</v>
+        <v>10.607900000000001</v>
       </c>
       <c r="W15" s="1">
-        <v>109.2889</v>
+        <v>11.8622</v>
       </c>
       <c r="X15" s="1">
-        <v>2.3506999999999998</v>
+        <v>10.133599999999999</v>
       </c>
       <c r="Y15" s="1">
-        <v>6.7076000000000002</v>
+        <v>6.2876000000000003</v>
       </c>
       <c r="Z15" s="1">
-        <v>6.9287000000000001</v>
+        <v>5.8699000000000003</v>
       </c>
       <c r="AA15" s="27">
-        <v>5.3962000000000003</v>
+        <v>3.8127</v>
       </c>
       <c r="AB15" s="1">
-        <v>32.713099999999997</v>
+        <v>4.2457000000000003</v>
       </c>
       <c r="AC15" s="1">
-        <v>74.917299999999997</v>
+        <v>1.3052999999999999</v>
       </c>
       <c r="AD15" s="1">
-        <v>32.198500000000003</v>
+        <v>1.4259999999999999</v>
       </c>
       <c r="AE15" s="1">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="AF15" s="1" t="s">
-        <v>1</v>
+        <v>49.551499999999997</v>
+      </c>
+      <c r="AF15" s="1">
+        <v>8.1311</v>
       </c>
       <c r="AG15" s="1">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="AH15" s="1">
+        <v>3.4502999999999999</v>
+      </c>
+      <c r="AI15" s="1">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="AJ15" s="1">
+        <v>0.30130000000000001</v>
+      </c>
+      <c r="AK15" s="1">
+        <v>2.6320000000000001</v>
+      </c>
+      <c r="AL15" s="1">
+        <v>1.9688000000000001</v>
+      </c>
+      <c r="AM15" s="1">
+        <v>13.6791</v>
+      </c>
+      <c r="AN15" s="1">
+        <v>4.5843999999999996</v>
+      </c>
+      <c r="AO15" s="1">
+        <v>25.884599999999999</v>
+      </c>
+      <c r="AP15" s="1">
+        <v>0.62990000000000002</v>
+      </c>
+      <c r="AQ15" s="1">
+        <v>1.9125000000000001</v>
+      </c>
+      <c r="AR15" s="1">
+        <v>8.4297000000000004</v>
+      </c>
+      <c r="AS15" s="1">
+        <v>32.302399999999999</v>
+      </c>
+      <c r="AT15" s="1">
+        <v>74.041200000000003</v>
+      </c>
+      <c r="AU15" s="1">
+        <v>60.860599999999998</v>
+      </c>
+      <c r="AV15" s="1">
+        <v>37.395099999999999</v>
+      </c>
+      <c r="AW15" s="27">
+        <v>2.3532999999999999</v>
+      </c>
+      <c r="AX15" s="27">
         <v>0</v>
       </c>
-      <c r="AH15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="1">
-        <v>3.1682000000000001</v>
-      </c>
-      <c r="AJ15" s="1">
-        <v>1.9974000000000001</v>
-      </c>
-      <c r="AK15" s="1">
-        <v>10.5509</v>
-      </c>
-      <c r="AL15" s="1">
-        <v>1.7723</v>
-      </c>
-      <c r="AM15" s="1">
-        <v>1.3877999999999999</v>
-      </c>
-      <c r="AN15" s="1">
-        <v>9.1791</v>
-      </c>
-      <c r="AO15" s="1">
-        <v>145.8621</v>
-      </c>
-      <c r="AP15" s="1">
-        <v>4.5934999999999997</v>
-      </c>
-      <c r="AQ15" s="1">
-        <v>4.5594000000000001</v>
-      </c>
-      <c r="AR15" s="1">
-        <v>1.6528</v>
-      </c>
-      <c r="AS15" s="1">
-        <v>89.885999999999996</v>
-      </c>
-      <c r="AT15" s="1">
-        <v>102.8505</v>
-      </c>
-      <c r="AU15" s="1">
-        <v>14.915800000000001</v>
-      </c>
-      <c r="AV15" s="1">
-        <v>37.524900000000002</v>
-      </c>
-      <c r="AW15" s="27">
-        <v>35.255200000000002</v>
-      </c>
-      <c r="AX15" s="27">
-        <v>132.15309999999999</v>
-      </c>
       <c r="AY15" s="1">
-        <v>1.8163</v>
+        <v>1.1181000000000001</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I17">
         <f>AVERAGEIF(E3:BA15, "&lt;=200")</f>
-        <v>4.3015851546391763</v>
+        <v>2.4103363095238088</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I18">
         <f>MEDIAN(E3:BA15)</f>
-        <v>0.74760000000000004</v>
+        <v>0.54830000000000001</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
@@ -38158,26 +38160,26 @@
         <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="H19" t="s">
         <v>5</v>
       </c>
       <c r="I19">
         <f>_xlfn.MAXIFS(E3:BA15, E3:BA15, "&lt;=200")</f>
-        <v>145.8621</v>
+        <v>74.041200000000003</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I20">
         <f>COUNTIF(E3:BA15, "&lt;=200") / (COUNT(E3:BA15) + COUNTIF(E3:BA15, "NaN")) * 100</f>
-        <v>93.810444874274651</v>
+        <v>98.82352941176471</v>
       </c>
     </row>
   </sheetData>
@@ -40348,12 +40350,12 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H25">
         <f>AVERAGEIF(D11:AZ23, "&lt;=200")</f>
@@ -40362,7 +40364,7 @@
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H26">
         <f>MEDIAN(D11:AZ23)</f>
@@ -40380,7 +40382,7 @@
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H28">
         <f>COUNTIF(D11:AZ23, "&lt;=200") / (COUNT(D11:AZ23) + COUNTIF(D11:AZ23, "NaN")) * 100</f>
